--- a/00_Data/Raw/Wind_Series/Varzea.xlsx
+++ b/00_Data/Raw/Wind_Series/Varzea.xlsx
@@ -6,28 +6,27 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">Data</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Geração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vento</t>
+    <t xml:space="preserve">Wind_speed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -64,7 +63,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,18 +361,12 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>30682</v>
       </c>
       <c r="B2" t="n">
-        <v>0.505112903225806</v>
-      </c>
-      <c r="C2" t="n">
         <v>7.24665725806452</v>
       </c>
     </row>
@@ -382,9 +375,6 @@
         <v>30713</v>
       </c>
       <c r="B3" t="n">
-        <v>0.545169540229885</v>
-      </c>
-      <c r="C3" t="n">
         <v>7.54513936781609</v>
       </c>
     </row>
@@ -393,9 +383,6 @@
         <v>30742</v>
       </c>
       <c r="B4" t="n">
-        <v>0.253047043010753</v>
-      </c>
-      <c r="C4" t="n">
         <v>5.29335215053763</v>
       </c>
     </row>
@@ -404,9 +391,6 @@
         <v>30773</v>
       </c>
       <c r="B5" t="n">
-        <v>0.314118055555556</v>
-      </c>
-      <c r="C5" t="n">
         <v>5.835125</v>
       </c>
     </row>
@@ -415,9 +399,6 @@
         <v>30803</v>
       </c>
       <c r="B6" t="n">
-        <v>0.522139784946237</v>
-      </c>
-      <c r="C6" t="n">
         <v>7.36873521505376</v>
       </c>
     </row>
@@ -426,9 +407,6 @@
         <v>30834</v>
       </c>
       <c r="B7" t="n">
-        <v>0.629020833333333</v>
-      </c>
-      <c r="C7" t="n">
         <v>8.12923055555556</v>
       </c>
     </row>
@@ -437,9 +415,6 @@
         <v>30864</v>
       </c>
       <c r="B8" t="n">
-        <v>0.691280913978495</v>
-      </c>
-      <c r="C8" t="n">
         <v>8.58493413978495</v>
       </c>
     </row>
@@ -448,9 +423,6 @@
         <v>30895</v>
       </c>
       <c r="B9" t="n">
-        <v>0.684470430107527</v>
-      </c>
-      <c r="C9" t="n">
         <v>8.54300134408602</v>
       </c>
     </row>
@@ -459,9 +431,6 @@
         <v>30926</v>
       </c>
       <c r="B10" t="n">
-        <v>0.648027777777778</v>
-      </c>
-      <c r="C10" t="n">
         <v>8.27633333333333</v>
       </c>
     </row>
@@ -470,9 +439,6 @@
         <v>30956</v>
       </c>
       <c r="B11" t="n">
-        <v>0.691381720430107</v>
-      </c>
-      <c r="C11" t="n">
         <v>8.65039112903226</v>
       </c>
     </row>
@@ -481,9 +447,6 @@
         <v>30987</v>
       </c>
       <c r="B12" t="n">
-        <v>0.652005555555556</v>
-      </c>
-      <c r="C12" t="n">
         <v>8.35142777777778</v>
       </c>
     </row>
@@ -492,9 +455,6 @@
         <v>31017</v>
       </c>
       <c r="B13" t="n">
-        <v>0.551086021505376</v>
-      </c>
-      <c r="C13" t="n">
         <v>7.55635080645161</v>
       </c>
     </row>
@@ -503,9 +463,6 @@
         <v>31048</v>
       </c>
       <c r="B14" t="n">
-        <v>0.352411290322581</v>
-      </c>
-      <c r="C14" t="n">
         <v>6.09914516129032</v>
       </c>
     </row>
@@ -514,9 +471,6 @@
         <v>31079</v>
       </c>
       <c r="B15" t="n">
-        <v>0.250821428571429</v>
-      </c>
-      <c r="C15" t="n">
         <v>5.33800446428571</v>
       </c>
     </row>
@@ -525,9 +479,6 @@
         <v>31107</v>
       </c>
       <c r="B16" t="n">
-        <v>0.23327688172043</v>
-      </c>
-      <c r="C16" t="n">
         <v>5.13457661290323</v>
       </c>
     </row>
@@ -536,9 +487,6 @@
         <v>31138</v>
       </c>
       <c r="B17" t="n">
-        <v>0.191656944444444</v>
-      </c>
-      <c r="C17" t="n">
         <v>4.673925</v>
       </c>
     </row>
@@ -547,9 +495,6 @@
         <v>31168</v>
       </c>
       <c r="B18" t="n">
-        <v>0.521864247311828</v>
-      </c>
-      <c r="C18" t="n">
         <v>7.36268413978495</v>
       </c>
     </row>
@@ -558,9 +503,6 @@
         <v>31199</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4974</v>
-      </c>
-      <c r="C19" t="n">
         <v>7.22913055555556</v>
       </c>
     </row>
@@ -569,9 +511,6 @@
         <v>31229</v>
       </c>
       <c r="B20" t="n">
-        <v>0.710911290322581</v>
-      </c>
-      <c r="C20" t="n">
         <v>8.95858602150538</v>
       </c>
     </row>
@@ -580,9 +519,6 @@
         <v>31260</v>
       </c>
       <c r="B21" t="n">
-        <v>0.690915322580645</v>
-      </c>
-      <c r="C21" t="n">
         <v>8.66604838709677</v>
       </c>
     </row>
@@ -591,9 +527,6 @@
         <v>31291</v>
       </c>
       <c r="B22" t="n">
-        <v>0.692540277777778</v>
-      </c>
-      <c r="C22" t="n">
         <v>8.65111666666667</v>
       </c>
     </row>
@@ -602,9 +535,6 @@
         <v>31321</v>
       </c>
       <c r="B23" t="n">
-        <v>0.642684139784946</v>
-      </c>
-      <c r="C23" t="n">
         <v>8.18523790322581</v>
       </c>
     </row>
@@ -613,9 +543,6 @@
         <v>31352</v>
       </c>
       <c r="B24" t="n">
-        <v>0.648257301808067</v>
-      </c>
-      <c r="C24" t="n">
         <v>8.39889290681502</v>
       </c>
     </row>
@@ -624,9 +551,6 @@
         <v>31382</v>
       </c>
       <c r="B25" t="n">
-        <v>0.515971774193548</v>
-      </c>
-      <c r="C25" t="n">
         <v>7.32368951612903</v>
       </c>
     </row>
@@ -635,9 +559,6 @@
         <v>31413</v>
       </c>
       <c r="B26" t="n">
-        <v>0.552904569892473</v>
-      </c>
-      <c r="C26" t="n">
         <v>7.63338306451613</v>
       </c>
     </row>
@@ -646,9 +567,6 @@
         <v>31444</v>
       </c>
       <c r="B27" t="n">
-        <v>0.361885416666667</v>
-      </c>
-      <c r="C27" t="n">
         <v>6.13859523809524</v>
       </c>
     </row>
@@ -657,9 +575,6 @@
         <v>31472</v>
       </c>
       <c r="B28" t="n">
-        <v>0.228540322580645</v>
-      </c>
-      <c r="C28" t="n">
         <v>5.07605107526882</v>
       </c>
     </row>
@@ -668,9 +583,6 @@
         <v>31503</v>
       </c>
       <c r="B29" t="n">
-        <v>0.383579166666667</v>
-      </c>
-      <c r="C29" t="n">
         <v>6.38887222222222</v>
       </c>
     </row>
@@ -679,9 +591,6 @@
         <v>31533</v>
       </c>
       <c r="B30" t="n">
-        <v>0.618737903225806</v>
-      </c>
-      <c r="C30" t="n">
         <v>8.04405107526882</v>
       </c>
     </row>
@@ -690,9 +599,6 @@
         <v>31564</v>
       </c>
       <c r="B31" t="n">
-        <v>0.727566666666667</v>
-      </c>
-      <c r="C31" t="n">
         <v>8.98633055555556</v>
       </c>
     </row>
@@ -701,9 +607,6 @@
         <v>31594</v>
       </c>
       <c r="B32" t="n">
-        <v>0.629963709677419</v>
-      </c>
-      <c r="C32" t="n">
         <v>8.15557258064516</v>
       </c>
     </row>
@@ -712,9 +615,6 @@
         <v>31625</v>
       </c>
       <c r="B33" t="n">
-        <v>0.637255376344086</v>
-      </c>
-      <c r="C33" t="n">
         <v>8.17947311827957</v>
       </c>
     </row>
@@ -723,9 +623,6 @@
         <v>31656</v>
       </c>
       <c r="B34" t="n">
-        <v>0.726379166666667</v>
-      </c>
-      <c r="C34" t="n">
         <v>8.88893194444444</v>
       </c>
     </row>
@@ -734,9 +631,6 @@
         <v>31686</v>
       </c>
       <c r="B35" t="n">
-        <v>0.643086137281292</v>
-      </c>
-      <c r="C35" t="n">
         <v>8.21082503364738</v>
       </c>
     </row>
@@ -745,9 +639,6 @@
         <v>31717</v>
       </c>
       <c r="B36" t="n">
-        <v>0.702525</v>
-      </c>
-      <c r="C36" t="n">
         <v>8.72990694444444</v>
       </c>
     </row>
@@ -756,9 +647,6 @@
         <v>31747</v>
       </c>
       <c r="B37" t="n">
-        <v>0.594842741935484</v>
-      </c>
-      <c r="C37" t="n">
         <v>7.89881989247312</v>
       </c>
     </row>
@@ -767,9 +655,6 @@
         <v>31778</v>
       </c>
       <c r="B38" t="n">
-        <v>0.556536290322581</v>
-      </c>
-      <c r="C38" t="n">
         <v>7.60475268817204</v>
       </c>
     </row>
@@ -778,9 +663,6 @@
         <v>31809</v>
       </c>
       <c r="B39" t="n">
-        <v>0.563160714285714</v>
-      </c>
-      <c r="C39" t="n">
         <v>7.67552380952381</v>
       </c>
     </row>
@@ -789,9 +671,6 @@
         <v>31837</v>
       </c>
       <c r="B40" t="n">
-        <v>0.277778225806452</v>
-      </c>
-      <c r="C40" t="n">
         <v>5.57004569892473</v>
       </c>
     </row>
@@ -800,9 +679,6 @@
         <v>31868</v>
       </c>
       <c r="B41" t="n">
-        <v>0.541820833333333</v>
-      </c>
-      <c r="C41" t="n">
         <v>7.53676111111111</v>
       </c>
     </row>
@@ -811,9 +687,6 @@
         <v>31898</v>
       </c>
       <c r="B42" t="n">
-        <v>0.579625</v>
-      </c>
-      <c r="C42" t="n">
         <v>7.7893938172043</v>
       </c>
     </row>
@@ -822,9 +695,6 @@
         <v>31929</v>
       </c>
       <c r="B43" t="n">
-        <v>0.608731944444444</v>
-      </c>
-      <c r="C43" t="n">
         <v>7.95703611111111</v>
       </c>
     </row>
@@ -833,9 +703,6 @@
         <v>31959</v>
       </c>
       <c r="B44" t="n">
-        <v>0.69566935483871</v>
-      </c>
-      <c r="C44" t="n">
         <v>8.63504032258064</v>
       </c>
     </row>
@@ -844,9 +711,6 @@
         <v>31990</v>
       </c>
       <c r="B45" t="n">
-        <v>0.686370967741936</v>
-      </c>
-      <c r="C45" t="n">
         <v>8.58814247311828</v>
       </c>
     </row>
@@ -855,9 +719,6 @@
         <v>32021</v>
       </c>
       <c r="B46" t="n">
-        <v>0.701683333333333</v>
-      </c>
-      <c r="C46" t="n">
         <v>8.67380416666667</v>
       </c>
     </row>
@@ -866,9 +727,6 @@
         <v>32051</v>
       </c>
       <c r="B47" t="n">
-        <v>0.631901749663526</v>
-      </c>
-      <c r="C47" t="n">
         <v>8.16110901749663</v>
       </c>
     </row>
@@ -877,9 +735,6 @@
         <v>32082</v>
       </c>
       <c r="B48" t="n">
-        <v>0.649643055555556</v>
-      </c>
-      <c r="C48" t="n">
         <v>8.30407222222222</v>
       </c>
     </row>
@@ -888,9 +743,6 @@
         <v>32112</v>
       </c>
       <c r="B49" t="n">
-        <v>0.661677419354839</v>
-      </c>
-      <c r="C49" t="n">
         <v>8.37628225806452</v>
       </c>
     </row>
@@ -899,9 +751,6 @@
         <v>32143</v>
       </c>
       <c r="B50" t="n">
-        <v>0.488423387096774</v>
-      </c>
-      <c r="C50" t="n">
         <v>7.13542204301075</v>
       </c>
     </row>
@@ -910,9 +759,6 @@
         <v>32174</v>
       </c>
       <c r="B51" t="n">
-        <v>0.490640804597701</v>
-      </c>
-      <c r="C51" t="n">
         <v>7.15530316091954</v>
       </c>
     </row>
@@ -921,9 +767,6 @@
         <v>32203</v>
       </c>
       <c r="B52" t="n">
-        <v>0.328060483870968</v>
-      </c>
-      <c r="C52" t="n">
         <v>5.89179704301075</v>
       </c>
     </row>
@@ -932,9 +775,6 @@
         <v>32234</v>
       </c>
       <c r="B53" t="n">
-        <v>0.355106944444444</v>
-      </c>
-      <c r="C53" t="n">
         <v>6.1603875</v>
       </c>
     </row>
@@ -943,9 +783,6 @@
         <v>32264</v>
       </c>
       <c r="B54" t="n">
-        <v>0.581407258064516</v>
-      </c>
-      <c r="C54" t="n">
         <v>7.76355913978495</v>
       </c>
     </row>
@@ -954,9 +791,6 @@
         <v>32295</v>
       </c>
       <c r="B55" t="n">
-        <v>0.687256944444444</v>
-      </c>
-      <c r="C55" t="n">
         <v>8.69023611111111</v>
       </c>
     </row>
@@ -965,9 +799,6 @@
         <v>32325</v>
       </c>
       <c r="B56" t="n">
-        <v>0.758461021505376</v>
-      </c>
-      <c r="C56" t="n">
         <v>9.34571908602151</v>
       </c>
     </row>
@@ -976,9 +807,6 @@
         <v>32356</v>
       </c>
       <c r="B57" t="n">
-        <v>0.772450268817204</v>
-      </c>
-      <c r="C57" t="n">
         <v>9.45521370967742</v>
       </c>
     </row>
@@ -987,9 +815,6 @@
         <v>32387</v>
       </c>
       <c r="B58" t="n">
-        <v>0.774343055555556</v>
-      </c>
-      <c r="C58" t="n">
         <v>9.39994583333333</v>
       </c>
     </row>
@@ -998,9 +823,6 @@
         <v>32417</v>
       </c>
       <c r="B59" t="n">
-        <v>0.676652759084791</v>
-      </c>
-      <c r="C59" t="n">
         <v>8.49231224764468</v>
       </c>
     </row>
@@ -1009,9 +831,6 @@
         <v>32448</v>
       </c>
       <c r="B60" t="n">
-        <v>0.659294444444444</v>
-      </c>
-      <c r="C60" t="n">
         <v>8.38163611111111</v>
       </c>
     </row>
@@ -1020,9 +839,6 @@
         <v>32478</v>
       </c>
       <c r="B61" t="n">
-        <v>0.516075268817204</v>
-      </c>
-      <c r="C61" t="n">
         <v>7.34497715053763</v>
       </c>
     </row>
@@ -1031,9 +847,6 @@
         <v>32509</v>
       </c>
       <c r="B62" t="n">
-        <v>0.50541935483871</v>
-      </c>
-      <c r="C62" t="n">
         <v>7.24910887096774</v>
       </c>
     </row>
@@ -1042,9 +855,6 @@
         <v>32540</v>
       </c>
       <c r="B63" t="n">
-        <v>0.516016369047619</v>
-      </c>
-      <c r="C63" t="n">
         <v>7.33310714285714</v>
       </c>
     </row>
@@ -1053,9 +863,6 @@
         <v>32568</v>
       </c>
       <c r="B64" t="n">
-        <v>0.355943548387097</v>
-      </c>
-      <c r="C64" t="n">
         <v>6.14102822580645</v>
       </c>
     </row>
@@ -1064,9 +871,6 @@
         <v>32599</v>
       </c>
       <c r="B65" t="n">
-        <v>0.226502777777778</v>
-      </c>
-      <c r="C65" t="n">
         <v>5.10353194444444</v>
       </c>
     </row>
@@ -1075,9 +879,6 @@
         <v>32629</v>
       </c>
       <c r="B66" t="n">
-        <v>0.431228494623656</v>
-      </c>
-      <c r="C66" t="n">
         <v>6.70110349462366</v>
       </c>
     </row>
@@ -1086,9 +887,6 @@
         <v>32660</v>
       </c>
       <c r="B67" t="n">
-        <v>0.533519444444444</v>
-      </c>
-      <c r="C67" t="n">
         <v>7.46314722222222</v>
       </c>
     </row>
@@ -1097,9 +895,6 @@
         <v>32690</v>
       </c>
       <c r="B68" t="n">
-        <v>0.604270161290323</v>
-      </c>
-      <c r="C68" t="n">
         <v>8.06736827956989</v>
       </c>
     </row>
@@ -1108,9 +903,6 @@
         <v>32721</v>
       </c>
       <c r="B69" t="n">
-        <v>0.715814516129032</v>
-      </c>
-      <c r="C69" t="n">
         <v>8.83873521505376</v>
       </c>
     </row>
@@ -1119,9 +911,6 @@
         <v>32752</v>
       </c>
       <c r="B70" t="n">
-        <v>0.635933333333333</v>
-      </c>
-      <c r="C70" t="n">
         <v>8.23782638888889</v>
       </c>
     </row>
@@ -1130,9 +919,6 @@
         <v>32782</v>
       </c>
       <c r="B71" t="n">
-        <v>0.684823687752355</v>
-      </c>
-      <c r="C71" t="n">
         <v>8.65179676985195</v>
       </c>
     </row>
@@ -1141,9 +927,6 @@
         <v>32813</v>
       </c>
       <c r="B72" t="n">
-        <v>0.627188888888889</v>
-      </c>
-      <c r="C72" t="n">
         <v>8.158625</v>
       </c>
     </row>
@@ -1152,9 +935,6 @@
         <v>32843</v>
       </c>
       <c r="B73" t="n">
-        <v>0.553123655913978</v>
-      </c>
-      <c r="C73" t="n">
         <v>7.60530241935484</v>
       </c>
     </row>
@@ -1163,9 +943,6 @@
         <v>32874</v>
       </c>
       <c r="B74" t="n">
-        <v>0.675100806451613</v>
-      </c>
-      <c r="C74" t="n">
         <v>8.50456586021505</v>
       </c>
     </row>
@@ -1174,9 +951,6 @@
         <v>32905</v>
       </c>
       <c r="B75" t="n">
-        <v>0.448654761904762</v>
-      </c>
-      <c r="C75" t="n">
         <v>6.90442708333333</v>
       </c>
     </row>
@@ -1185,9 +959,6 @@
         <v>32933</v>
       </c>
       <c r="B76" t="n">
-        <v>0.585138440860215</v>
-      </c>
-      <c r="C76" t="n">
         <v>7.81097580645161</v>
       </c>
     </row>
@@ -1196,9 +967,6 @@
         <v>32964</v>
       </c>
       <c r="B77" t="n">
-        <v>0.575501388888889</v>
-      </c>
-      <c r="C77" t="n">
         <v>7.76167361111111</v>
       </c>
     </row>
@@ -1207,9 +975,6 @@
         <v>32994</v>
       </c>
       <c r="B78" t="n">
-        <v>0.530709677419355</v>
-      </c>
-      <c r="C78" t="n">
         <v>7.44731048387097</v>
       </c>
     </row>
@@ -1218,9 +983,6 @@
         <v>33025</v>
       </c>
       <c r="B79" t="n">
-        <v>0.691763888888889</v>
-      </c>
-      <c r="C79" t="n">
         <v>8.62630416666667</v>
       </c>
     </row>
@@ -1229,9 +991,6 @@
         <v>33055</v>
       </c>
       <c r="B80" t="n">
-        <v>0.620258064516129</v>
-      </c>
-      <c r="C80" t="n">
         <v>8.08822983870968</v>
       </c>
     </row>
@@ -1240,9 +999,6 @@
         <v>33086</v>
       </c>
       <c r="B81" t="n">
-        <v>0.722331989247312</v>
-      </c>
-      <c r="C81" t="n">
         <v>8.84949596774194</v>
       </c>
     </row>
@@ -1251,9 +1007,6 @@
         <v>33117</v>
       </c>
       <c r="B82" t="n">
-        <v>0.665533333333333</v>
-      </c>
-      <c r="C82" t="n">
         <v>8.40860972222222</v>
       </c>
     </row>
@@ -1262,9 +1015,6 @@
         <v>33147</v>
       </c>
       <c r="B83" t="n">
-        <v>0.693485868102288</v>
-      </c>
-      <c r="C83" t="n">
         <v>8.65394212651413</v>
       </c>
     </row>
@@ -1273,9 +1023,6 @@
         <v>33178</v>
       </c>
       <c r="B84" t="n">
-        <v>0.646788888888889</v>
-      </c>
-      <c r="C84" t="n">
         <v>8.30610277777778</v>
       </c>
     </row>
@@ -1284,9 +1031,6 @@
         <v>33208</v>
       </c>
       <c r="B85" t="n">
-        <v>0.595658602150538</v>
-      </c>
-      <c r="C85" t="n">
         <v>7.8754247311828</v>
       </c>
     </row>
@@ -1295,9 +1039,6 @@
         <v>33239</v>
       </c>
       <c r="B86" t="n">
-        <v>0.540569892473118</v>
-      </c>
-      <c r="C86" t="n">
         <v>7.50171370967742</v>
       </c>
     </row>
@@ -1306,9 +1047,6 @@
         <v>33270</v>
       </c>
       <c r="B87" t="n">
-        <v>0.478431547619048</v>
-      </c>
-      <c r="C87" t="n">
         <v>7.06522916666667</v>
       </c>
     </row>
@@ -1317,9 +1055,6 @@
         <v>33298</v>
       </c>
       <c r="B88" t="n">
-        <v>0.482073924731183</v>
-      </c>
-      <c r="C88" t="n">
         <v>7.10381720430107</v>
       </c>
     </row>
@@ -1328,9 +1063,6 @@
         <v>33329</v>
       </c>
       <c r="B89" t="n">
-        <v>0.445322222222222</v>
-      </c>
-      <c r="C89" t="n">
         <v>6.80029861111111</v>
       </c>
     </row>
@@ -1339,9 +1071,6 @@
         <v>33359</v>
       </c>
       <c r="B90" t="n">
-        <v>0.577452956989247</v>
-      </c>
-      <c r="C90" t="n">
         <v>7.81344220430107</v>
       </c>
     </row>
@@ -1350,9 +1079,6 @@
         <v>33390</v>
       </c>
       <c r="B91" t="n">
-        <v>0.710601388888889</v>
-      </c>
-      <c r="C91" t="n">
         <v>8.79186388888889</v>
       </c>
     </row>
@@ -1361,9 +1087,6 @@
         <v>33420</v>
       </c>
       <c r="B92" t="n">
-        <v>0.771844086021505</v>
-      </c>
-      <c r="C92" t="n">
         <v>9.44630913978495</v>
       </c>
     </row>
@@ -1372,9 +1095,6 @@
         <v>33451</v>
       </c>
       <c r="B93" t="n">
-        <v>0.787791666666667</v>
-      </c>
-      <c r="C93" t="n">
         <v>9.60154704301075</v>
       </c>
     </row>
@@ -1383,9 +1103,6 @@
         <v>33482</v>
       </c>
       <c r="B94" t="n">
-        <v>0.7072125</v>
-      </c>
-      <c r="C94" t="n">
         <v>8.79350555555556</v>
       </c>
     </row>
@@ -1394,9 +1111,6 @@
         <v>33512</v>
       </c>
       <c r="B95" t="n">
-        <v>0.723705248990579</v>
-      </c>
-      <c r="C95" t="n">
         <v>8.91948586810229</v>
       </c>
     </row>
@@ -1405,9 +1119,6 @@
         <v>33543</v>
       </c>
       <c r="B96" t="n">
-        <v>0.614054166666667</v>
-      </c>
-      <c r="C96" t="n">
         <v>8.04811666666667</v>
       </c>
     </row>
@@ -1416,9 +1127,6 @@
         <v>33573</v>
       </c>
       <c r="B97" t="n">
-        <v>0.566447580645161</v>
-      </c>
-      <c r="C97" t="n">
         <v>7.68932930107527</v>
       </c>
     </row>
@@ -1427,9 +1135,6 @@
         <v>33604</v>
       </c>
       <c r="B98" t="n">
-        <v>0.482514784946237</v>
-      </c>
-      <c r="C98" t="n">
         <v>7.11892338709677</v>
       </c>
     </row>
@@ -1438,9 +1143,6 @@
         <v>33635</v>
       </c>
       <c r="B99" t="n">
-        <v>0.559465517241379</v>
-      </c>
-      <c r="C99" t="n">
         <v>7.61933908045977</v>
       </c>
     </row>
@@ -1449,9 +1151,6 @@
         <v>33664</v>
       </c>
       <c r="B100" t="n">
-        <v>0.604672043010753</v>
-      </c>
-      <c r="C100" t="n">
         <v>8.01536962365591</v>
       </c>
     </row>
@@ -1460,9 +1159,6 @@
         <v>33695</v>
       </c>
       <c r="B101" t="n">
-        <v>0.542306944444444</v>
-      </c>
-      <c r="C101" t="n">
         <v>7.5365875</v>
       </c>
     </row>
@@ -1471,9 +1167,6 @@
         <v>33725</v>
       </c>
       <c r="B102" t="n">
-        <v>0.561133064516129</v>
-      </c>
-      <c r="C102" t="n">
         <v>7.64314650537634</v>
       </c>
     </row>
@@ -1482,9 +1175,6 @@
         <v>33756</v>
       </c>
       <c r="B103" t="n">
-        <v>0.649909722222222</v>
-      </c>
-      <c r="C103" t="n">
         <v>8.26668472222222</v>
       </c>
     </row>
@@ -1493,9 +1183,6 @@
         <v>33786</v>
       </c>
       <c r="B104" t="n">
-        <v>0.676998655913978</v>
-      </c>
-      <c r="C104" t="n">
         <v>8.48705510752688</v>
       </c>
     </row>
@@ -1504,9 +1191,6 @@
         <v>33817</v>
       </c>
       <c r="B105" t="n">
-        <v>0.715338709677419</v>
-      </c>
-      <c r="C105" t="n">
         <v>8.82546370967742</v>
       </c>
     </row>
@@ -1515,9 +1199,6 @@
         <v>33848</v>
       </c>
       <c r="B106" t="n">
-        <v>0.741109722222222</v>
-      </c>
-      <c r="C106" t="n">
         <v>9.00167638888889</v>
       </c>
     </row>
@@ -1526,9 +1207,6 @@
         <v>33878</v>
       </c>
       <c r="B107" t="n">
-        <v>0.721921938088829</v>
-      </c>
-      <c r="C107" t="n">
         <v>8.87192866756393</v>
       </c>
     </row>
@@ -1537,9 +1215,6 @@
         <v>33909</v>
       </c>
       <c r="B108" t="n">
-        <v>0.664463888888889</v>
-      </c>
-      <c r="C108" t="n">
         <v>8.39917638888889</v>
       </c>
     </row>
@@ -1548,9 +1223,6 @@
         <v>33939</v>
       </c>
       <c r="B109" t="n">
-        <v>0.609961021505376</v>
-      </c>
-      <c r="C109" t="n">
         <v>8.03581317204301</v>
       </c>
     </row>
@@ -1559,9 +1231,6 @@
         <v>33970</v>
       </c>
       <c r="B110" t="n">
-        <v>0.583162634408602</v>
-      </c>
-      <c r="C110" t="n">
         <v>7.85236155913979</v>
       </c>
     </row>
@@ -1570,9 +1239,6 @@
         <v>34001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.565571428571429</v>
-      </c>
-      <c r="C111" t="n">
         <v>7.67486607142857</v>
       </c>
     </row>
@@ -1581,9 +1247,6 @@
         <v>34029</v>
       </c>
       <c r="B112" t="n">
-        <v>0.580126344086021</v>
-      </c>
-      <c r="C112" t="n">
         <v>7.77169086021505</v>
       </c>
     </row>
@@ -1592,9 +1255,6 @@
         <v>34060</v>
       </c>
       <c r="B113" t="n">
-        <v>0.573283333333333</v>
-      </c>
-      <c r="C113" t="n">
         <v>7.71917777777778</v>
       </c>
     </row>
@@ -1603,9 +1263,6 @@
         <v>34090</v>
       </c>
       <c r="B114" t="n">
-        <v>0.631650537634409</v>
-      </c>
-      <c r="C114" t="n">
         <v>8.19592204301075</v>
       </c>
     </row>
@@ -1614,9 +1271,6 @@
         <v>34121</v>
       </c>
       <c r="B115" t="n">
-        <v>0.696816666666667</v>
-      </c>
-      <c r="C115" t="n">
         <v>8.64904722222222</v>
       </c>
     </row>
@@ -1625,9 +1279,6 @@
         <v>34151</v>
       </c>
       <c r="B116" t="n">
-        <v>0.700716397849462</v>
-      </c>
-      <c r="C116" t="n">
         <v>8.72187768817204</v>
       </c>
     </row>
@@ -1636,9 +1287,6 @@
         <v>34182</v>
       </c>
       <c r="B117" t="n">
-        <v>0.697465053763441</v>
-      </c>
-      <c r="C117" t="n">
         <v>8.65411155913979</v>
       </c>
     </row>
@@ -1647,9 +1295,6 @@
         <v>34213</v>
       </c>
       <c r="B118" t="n">
-        <v>0.631541666666667</v>
-      </c>
-      <c r="C118" t="n">
         <v>8.16228333333333</v>
       </c>
     </row>
@@ -1658,9 +1303,6 @@
         <v>34243</v>
       </c>
       <c r="B119" t="n">
-        <v>0.687970390309556</v>
-      </c>
-      <c r="C119" t="n">
         <v>8.7499932705249</v>
       </c>
     </row>
@@ -1669,9 +1311,6 @@
         <v>34274</v>
       </c>
       <c r="B120" t="n">
-        <v>0.692002777777778</v>
-      </c>
-      <c r="C120" t="n">
         <v>8.75657361111111</v>
       </c>
     </row>
@@ -1680,9 +1319,6 @@
         <v>34304</v>
       </c>
       <c r="B121" t="n">
-        <v>0.642465053763441</v>
-      </c>
-      <c r="C121" t="n">
         <v>8.26659811827957</v>
       </c>
     </row>
@@ -1691,9 +1327,6 @@
         <v>34335</v>
       </c>
       <c r="B122" t="n">
-        <v>0.456577956989247</v>
-      </c>
-      <c r="C122" t="n">
         <v>6.91245564516129</v>
       </c>
     </row>
@@ -1702,9 +1335,6 @@
         <v>34366</v>
       </c>
       <c r="B123" t="n">
-        <v>0.508224702380952</v>
-      </c>
-      <c r="C123" t="n">
         <v>7.27116666666667</v>
       </c>
     </row>
@@ -1713,9 +1343,6 @@
         <v>34394</v>
       </c>
       <c r="B124" t="n">
-        <v>0.404883064516129</v>
-      </c>
-      <c r="C124" t="n">
         <v>6.53439919354839</v>
       </c>
     </row>
@@ -1724,9 +1351,6 @@
         <v>34425</v>
       </c>
       <c r="B125" t="n">
-        <v>0.465673611111111</v>
-      </c>
-      <c r="C125" t="n">
         <v>6.93954444444444</v>
       </c>
     </row>
@@ -1735,9 +1359,6 @@
         <v>34455</v>
       </c>
       <c r="B126" t="n">
-        <v>0.579045698924731</v>
-      </c>
-      <c r="C126" t="n">
         <v>7.77972849462366</v>
       </c>
     </row>
@@ -1746,9 +1367,6 @@
         <v>34486</v>
       </c>
       <c r="B127" t="n">
-        <v>0.543622222222222</v>
-      </c>
-      <c r="C127" t="n">
         <v>7.529325</v>
       </c>
     </row>
@@ -1757,9 +1375,6 @@
         <v>34516</v>
       </c>
       <c r="B128" t="n">
-        <v>0.732068548387097</v>
-      </c>
-      <c r="C128" t="n">
         <v>8.93963709677419</v>
       </c>
     </row>
@@ -1768,9 +1383,6 @@
         <v>34547</v>
       </c>
       <c r="B129" t="n">
-        <v>0.736701612903226</v>
-      </c>
-      <c r="C129" t="n">
         <v>9.02098252688172</v>
       </c>
     </row>
@@ -1779,9 +1391,6 @@
         <v>34578</v>
       </c>
       <c r="B130" t="n">
-        <v>0.758580555555556</v>
-      </c>
-      <c r="C130" t="n">
         <v>9.20721527777778</v>
       </c>
     </row>
@@ -1790,9 +1399,6 @@
         <v>34608</v>
       </c>
       <c r="B131" t="n">
-        <v>0.718388963660834</v>
-      </c>
-      <c r="C131" t="n">
         <v>8.93326244952894</v>
       </c>
     </row>
@@ -1801,9 +1407,6 @@
         <v>34639</v>
       </c>
       <c r="B132" t="n">
-        <v>0.691244444444444</v>
-      </c>
-      <c r="C132" t="n">
         <v>8.6122125</v>
       </c>
     </row>
@@ -1812,9 +1415,6 @@
         <v>34669</v>
       </c>
       <c r="B133" t="n">
-        <v>0.633622311827957</v>
-      </c>
-      <c r="C133" t="n">
         <v>8.23576075268817</v>
       </c>
     </row>
@@ -1823,9 +1423,6 @@
         <v>34700</v>
       </c>
       <c r="B134" t="n">
-        <v>0.527490591397849</v>
-      </c>
-      <c r="C134" t="n">
         <v>7.40229569892473</v>
       </c>
     </row>
@@ -1834,9 +1431,6 @@
         <v>34731</v>
       </c>
       <c r="B135" t="n">
-        <v>0.365494047619048</v>
-      </c>
-      <c r="C135" t="n">
         <v>6.22691964285714</v>
       </c>
     </row>
@@ -1845,9 +1439,6 @@
         <v>34759</v>
       </c>
       <c r="B136" t="n">
-        <v>0.447029569892473</v>
-      </c>
-      <c r="C136" t="n">
         <v>6.81022177419355</v>
       </c>
     </row>
@@ -1856,9 +1447,6 @@
         <v>34790</v>
       </c>
       <c r="B137" t="n">
-        <v>0.4197625</v>
-      </c>
-      <c r="C137" t="n">
         <v>6.63607361111111</v>
       </c>
     </row>
@@ -1867,9 +1455,6 @@
         <v>34820</v>
       </c>
       <c r="B138" t="n">
-        <v>0.451096774193548</v>
-      </c>
-      <c r="C138" t="n">
         <v>6.86858602150538</v>
       </c>
     </row>
@@ -1878,9 +1463,6 @@
         <v>34851</v>
       </c>
       <c r="B139" t="n">
-        <v>0.679456944444444</v>
-      </c>
-      <c r="C139" t="n">
         <v>8.54854027777778</v>
       </c>
     </row>
@@ -1889,9 +1471,6 @@
         <v>34881</v>
       </c>
       <c r="B140" t="n">
-        <v>0.755650537634409</v>
-      </c>
-      <c r="C140" t="n">
         <v>9.24022177419355</v>
       </c>
     </row>
@@ -1900,9 +1479,6 @@
         <v>34912</v>
       </c>
       <c r="B141" t="n">
-        <v>0.775862903225806</v>
-      </c>
-      <c r="C141" t="n">
         <v>9.34448655913978</v>
       </c>
     </row>
@@ -1911,9 +1487,6 @@
         <v>34943</v>
       </c>
       <c r="B142" t="n">
-        <v>0.793245833333333</v>
-      </c>
-      <c r="C142" t="n">
         <v>9.579625</v>
       </c>
     </row>
@@ -1922,9 +1495,6 @@
         <v>34973</v>
       </c>
       <c r="B143" t="n">
-        <v>0.675332436069986</v>
-      </c>
-      <c r="C143" t="n">
         <v>8.57954777927322</v>
       </c>
     </row>
@@ -1933,9 +1503,6 @@
         <v>35004</v>
       </c>
       <c r="B144" t="n">
-        <v>0.645995833333333</v>
-      </c>
-      <c r="C144" t="n">
         <v>8.33814027777778</v>
       </c>
     </row>
@@ -1944,9 +1511,6 @@
         <v>35034</v>
       </c>
       <c r="B145" t="n">
-        <v>0.537826612903226</v>
-      </c>
-      <c r="C145" t="n">
         <v>7.48081586021505</v>
       </c>
     </row>
@@ -1955,9 +1519,6 @@
         <v>35065</v>
       </c>
       <c r="B146" t="n">
-        <v>0.579424731182796</v>
-      </c>
-      <c r="C146" t="n">
         <v>7.76349327956989</v>
       </c>
     </row>
@@ -1966,9 +1527,6 @@
         <v>35096</v>
       </c>
       <c r="B147" t="n">
-        <v>0.528586206896552</v>
-      </c>
-      <c r="C147" t="n">
         <v>7.41602011494253</v>
       </c>
     </row>
@@ -1977,9 +1535,6 @@
         <v>35125</v>
       </c>
       <c r="B148" t="n">
-        <v>0.321413978494624</v>
-      </c>
-      <c r="C148" t="n">
         <v>5.85408870967742</v>
       </c>
     </row>
@@ -1988,9 +1543,6 @@
         <v>35156</v>
       </c>
       <c r="B149" t="n">
-        <v>0.2856125</v>
-      </c>
-      <c r="C149" t="n">
         <v>5.48129444444444</v>
       </c>
     </row>
@@ -1999,9 +1551,6 @@
         <v>35186</v>
       </c>
       <c r="B150" t="n">
-        <v>0.47465188172043</v>
-      </c>
-      <c r="C150" t="n">
         <v>7.0041438172043</v>
       </c>
     </row>
@@ -2010,9 +1559,6 @@
         <v>35217</v>
       </c>
       <c r="B151" t="n">
-        <v>0.708688888888889</v>
-      </c>
-      <c r="C151" t="n">
         <v>8.84184444444444</v>
       </c>
     </row>
@@ -2021,9 +1567,6 @@
         <v>35247</v>
       </c>
       <c r="B152" t="n">
-        <v>0.742869623655914</v>
-      </c>
-      <c r="C152" t="n">
         <v>9.18921505376344</v>
       </c>
     </row>
@@ -2032,9 +1575,6 @@
         <v>35278</v>
       </c>
       <c r="B153" t="n">
-        <v>0.73270564516129</v>
-      </c>
-      <c r="C153" t="n">
         <v>9.0205873655914</v>
       </c>
     </row>
@@ -2043,9 +1583,6 @@
         <v>35309</v>
       </c>
       <c r="B154" t="n">
-        <v>0.763416666666667</v>
-      </c>
-      <c r="C154" t="n">
         <v>9.3493625</v>
       </c>
     </row>
@@ -2054,9 +1591,6 @@
         <v>35339</v>
       </c>
       <c r="B155" t="n">
-        <v>0.710100942126514</v>
-      </c>
-      <c r="C155" t="n">
         <v>8.77748183041723</v>
       </c>
     </row>
@@ -2065,9 +1599,6 @@
         <v>35370</v>
       </c>
       <c r="B156" t="n">
-        <v>0.608129166666667</v>
-      </c>
-      <c r="C156" t="n">
         <v>8.02831944444444</v>
       </c>
     </row>
@@ -2076,9 +1607,6 @@
         <v>35400</v>
       </c>
       <c r="B157" t="n">
-        <v>0.600037634408602</v>
-      </c>
-      <c r="C157" t="n">
         <v>7.92850403225806</v>
       </c>
     </row>
@@ -2087,9 +1615,6 @@
         <v>35431</v>
       </c>
       <c r="B158" t="n">
-        <v>0.572501344086021</v>
-      </c>
-      <c r="C158" t="n">
         <v>7.7188064516129</v>
       </c>
     </row>
@@ -2098,9 +1623,6 @@
         <v>35462</v>
       </c>
       <c r="B159" t="n">
-        <v>0.686534226190476</v>
-      </c>
-      <c r="C159" t="n">
         <v>8.56160714285714</v>
       </c>
     </row>
@@ -2109,9 +1631,6 @@
         <v>35490</v>
       </c>
       <c r="B160" t="n">
-        <v>0.480474462365591</v>
-      </c>
-      <c r="C160" t="n">
         <v>7.10608064516129</v>
       </c>
     </row>
@@ -2120,9 +1639,6 @@
         <v>35521</v>
       </c>
       <c r="B161" t="n">
-        <v>0.467533333333333</v>
-      </c>
-      <c r="C161" t="n">
         <v>6.98316805555556</v>
       </c>
     </row>
@@ -2131,9 +1647,6 @@
         <v>35551</v>
       </c>
       <c r="B162" t="n">
-        <v>0.620788978494624</v>
-      </c>
-      <c r="C162" t="n">
         <v>8.13366935483871</v>
       </c>
     </row>
@@ -2142,9 +1655,6 @@
         <v>35582</v>
       </c>
       <c r="B163" t="n">
-        <v>0.605548611111111</v>
-      </c>
-      <c r="C163" t="n">
         <v>7.92891944444444</v>
       </c>
     </row>
@@ -2153,9 +1663,6 @@
         <v>35612</v>
       </c>
       <c r="B164" t="n">
-        <v>0.732127688172043</v>
-      </c>
-      <c r="C164" t="n">
         <v>8.97015591397849</v>
       </c>
     </row>
@@ -2164,9 +1671,6 @@
         <v>35643</v>
       </c>
       <c r="B165" t="n">
-        <v>0.770950268817204</v>
-      </c>
-      <c r="C165" t="n">
         <v>9.41059005376344</v>
       </c>
     </row>
@@ -2175,9 +1679,6 @@
         <v>35674</v>
       </c>
       <c r="B166" t="n">
-        <v>0.605929166666667</v>
-      </c>
-      <c r="C166" t="n">
         <v>7.97205</v>
       </c>
     </row>
@@ -2186,9 +1687,6 @@
         <v>35704</v>
       </c>
       <c r="B167" t="n">
-        <v>0.610609690444145</v>
-      </c>
-      <c r="C167" t="n">
         <v>8.03225706594886</v>
       </c>
     </row>
@@ -2197,9 +1695,6 @@
         <v>35735</v>
       </c>
       <c r="B168" t="n">
-        <v>0.604344444444444</v>
-      </c>
-      <c r="C168" t="n">
         <v>7.97531527777778</v>
       </c>
     </row>
@@ -2208,9 +1703,6 @@
         <v>35765</v>
       </c>
       <c r="B169" t="n">
-        <v>0.502721774193548</v>
-      </c>
-      <c r="C169" t="n">
         <v>7.23279435483871</v>
       </c>
     </row>
@@ -2219,9 +1711,6 @@
         <v>35796</v>
       </c>
       <c r="B170" t="n">
-        <v>0.442646505376344</v>
-      </c>
-      <c r="C170" t="n">
         <v>6.81609408602151</v>
       </c>
     </row>
@@ -2230,9 +1719,6 @@
         <v>35827</v>
       </c>
       <c r="B171" t="n">
-        <v>0.58852380952381</v>
-      </c>
-      <c r="C171" t="n">
         <v>7.83109077380952</v>
       </c>
     </row>
@@ -2241,9 +1727,6 @@
         <v>35855</v>
       </c>
       <c r="B172" t="n">
-        <v>0.532431451612903</v>
-      </c>
-      <c r="C172" t="n">
         <v>7.47637231182796</v>
       </c>
     </row>
@@ -2252,9 +1735,6 @@
         <v>35886</v>
       </c>
       <c r="B173" t="n">
-        <v>0.646156944444444</v>
-      </c>
-      <c r="C173" t="n">
         <v>8.26400138888889</v>
       </c>
     </row>
@@ -2263,9 +1743,6 @@
         <v>35916</v>
       </c>
       <c r="B174" t="n">
-        <v>0.658741935483871</v>
-      </c>
-      <c r="C174" t="n">
         <v>8.41097983870968</v>
       </c>
     </row>
@@ -2274,9 +1751,6 @@
         <v>35947</v>
       </c>
       <c r="B175" t="n">
-        <v>0.739436111111111</v>
-      </c>
-      <c r="C175" t="n">
         <v>9.08106944444445</v>
       </c>
     </row>
@@ -2285,9 +1759,6 @@
         <v>35977</v>
       </c>
       <c r="B176" t="n">
-        <v>0.723060483870968</v>
-      </c>
-      <c r="C176" t="n">
         <v>8.93351075268817</v>
       </c>
     </row>
@@ -2296,9 +1767,6 @@
         <v>36008</v>
       </c>
       <c r="B177" t="n">
-        <v>0.754891129032258</v>
-      </c>
-      <c r="C177" t="n">
         <v>9.15608467741935</v>
       </c>
     </row>
@@ -2307,9 +1775,6 @@
         <v>36039</v>
       </c>
       <c r="B178" t="n">
-        <v>0.756708333333333</v>
-      </c>
-      <c r="C178" t="n">
         <v>9.20321944444444</v>
       </c>
     </row>
@@ -2318,9 +1783,6 @@
         <v>36069</v>
       </c>
       <c r="B179" t="n">
-        <v>0.750718707940781</v>
-      </c>
-      <c r="C179" t="n">
         <v>9.14073889636608</v>
       </c>
     </row>
@@ -2329,9 +1791,6 @@
         <v>36100</v>
       </c>
       <c r="B180" t="n">
-        <v>0.606993055555556</v>
-      </c>
-      <c r="C180" t="n">
         <v>7.978125</v>
       </c>
     </row>
@@ -2340,9 +1799,6 @@
         <v>36130</v>
       </c>
       <c r="B181" t="n">
-        <v>0.658922043010753</v>
-      </c>
-      <c r="C181" t="n">
         <v>8.36958064516129</v>
       </c>
     </row>
@@ -2351,9 +1807,6 @@
         <v>36161</v>
       </c>
       <c r="B182" t="n">
-        <v>0.571655913978495</v>
-      </c>
-      <c r="C182" t="n">
         <v>7.71070161290323</v>
       </c>
     </row>
@@ -2362,9 +1815,6 @@
         <v>36192</v>
       </c>
       <c r="B183" t="n">
-        <v>0.631175595238095</v>
-      </c>
-      <c r="C183" t="n">
         <v>8.17315476190476</v>
       </c>
     </row>
@@ -2373,9 +1823,6 @@
         <v>36220</v>
       </c>
       <c r="B184" t="n">
-        <v>0.50873252688172</v>
-      </c>
-      <c r="C184" t="n">
         <v>7.2664126344086</v>
       </c>
     </row>
@@ -2384,9 +1831,6 @@
         <v>36251</v>
       </c>
       <c r="B185" t="n">
-        <v>0.589409722222222</v>
-      </c>
-      <c r="C185" t="n">
         <v>7.81948472222222</v>
       </c>
     </row>
@@ -2395,9 +1839,6 @@
         <v>36281</v>
       </c>
       <c r="B186" t="n">
-        <v>0.548956989247312</v>
-      </c>
-      <c r="C186" t="n">
         <v>7.58728629032258</v>
       </c>
     </row>
@@ -2406,9 +1847,6 @@
         <v>36312</v>
       </c>
       <c r="B187" t="n">
-        <v>0.671970833333333</v>
-      </c>
-      <c r="C187" t="n">
         <v>8.49809583333333</v>
       </c>
     </row>
@@ -2417,9 +1855,6 @@
         <v>36342</v>
       </c>
       <c r="B188" t="n">
-        <v>0.780091397849462</v>
-      </c>
-      <c r="C188" t="n">
         <v>9.52121102150538</v>
       </c>
     </row>
@@ -2428,9 +1863,6 @@
         <v>36373</v>
       </c>
       <c r="B189" t="n">
-        <v>0.804158602150538</v>
-      </c>
-      <c r="C189" t="n">
         <v>9.75734946236559</v>
       </c>
     </row>
@@ -2439,9 +1871,6 @@
         <v>36404</v>
       </c>
       <c r="B190" t="n">
-        <v>0.76885</v>
-      </c>
-      <c r="C190" t="n">
         <v>9.39219722222222</v>
       </c>
     </row>
@@ -2450,9 +1879,6 @@
         <v>36434</v>
       </c>
       <c r="B191" t="n">
-        <v>0.683650067294751</v>
-      </c>
-      <c r="C191" t="n">
         <v>8.66255181695828</v>
       </c>
     </row>
@@ -2461,9 +1887,6 @@
         <v>36465</v>
       </c>
       <c r="B192" t="n">
-        <v>0.60895</v>
-      </c>
-      <c r="C192" t="n">
         <v>7.99496111111111</v>
       </c>
     </row>
@@ -2472,9 +1895,6 @@
         <v>36495</v>
       </c>
       <c r="B193" t="n">
-        <v>0.629634408602151</v>
-      </c>
-      <c r="C193" t="n">
         <v>8.20647715053764</v>
       </c>
     </row>
@@ -2483,9 +1903,6 @@
         <v>36526</v>
       </c>
       <c r="B194" t="n">
-        <v>0.51404435483871</v>
-      </c>
-      <c r="C194" t="n">
         <v>7.31231720430107</v>
       </c>
     </row>
@@ -2494,9 +1911,6 @@
         <v>36557</v>
       </c>
       <c r="B195" t="n">
-        <v>0.385522988505747</v>
-      </c>
-      <c r="C195" t="n">
         <v>6.24241810344828</v>
       </c>
     </row>
@@ -2505,9 +1919,6 @@
         <v>36586</v>
       </c>
       <c r="B196" t="n">
-        <v>0.558823924731183</v>
-      </c>
-      <c r="C196" t="n">
         <v>7.6073561827957</v>
       </c>
     </row>
@@ -2516,9 +1927,6 @@
         <v>36617</v>
       </c>
       <c r="B197" t="n">
-        <v>0.503090277777778</v>
-      </c>
-      <c r="C197" t="n">
         <v>7.14664305555556</v>
       </c>
     </row>
@@ -2527,9 +1935,6 @@
         <v>36647</v>
       </c>
       <c r="B198" t="n">
-        <v>0.618829301075269</v>
-      </c>
-      <c r="C198" t="n">
         <v>8.08488306451613</v>
       </c>
     </row>
@@ -2538,9 +1943,6 @@
         <v>36678</v>
       </c>
       <c r="B199" t="n">
-        <v>0.638265277777778</v>
-      </c>
-      <c r="C199" t="n">
         <v>8.26816388888889</v>
       </c>
     </row>
@@ -2549,9 +1951,6 @@
         <v>36708</v>
       </c>
       <c r="B200" t="n">
-        <v>0.689680107526882</v>
-      </c>
-      <c r="C200" t="n">
         <v>8.68064784946237</v>
       </c>
     </row>
@@ -2560,9 +1959,6 @@
         <v>36739</v>
       </c>
       <c r="B201" t="n">
-        <v>0.711439516129032</v>
-      </c>
-      <c r="C201" t="n">
         <v>8.85686021505376</v>
       </c>
     </row>
@@ -2571,9 +1967,6 @@
         <v>36770</v>
       </c>
       <c r="B202" t="n">
-        <v>0.721230555555556</v>
-      </c>
-      <c r="C202" t="n">
         <v>8.93516666666667</v>
       </c>
     </row>
@@ -2582,9 +1975,6 @@
         <v>36800</v>
       </c>
       <c r="B203" t="n">
-        <v>0.726049798115747</v>
-      </c>
-      <c r="C203" t="n">
         <v>8.97364737550471</v>
       </c>
     </row>
@@ -2593,9 +1983,6 @@
         <v>36831</v>
       </c>
       <c r="B204" t="n">
-        <v>0.616136111111111</v>
-      </c>
-      <c r="C204" t="n">
         <v>8.08473055555556</v>
       </c>
     </row>
@@ -2604,9 +1991,6 @@
         <v>36861</v>
       </c>
       <c r="B205" t="n">
-        <v>0.51780376344086</v>
-      </c>
-      <c r="C205" t="n">
         <v>7.31883333333333</v>
       </c>
     </row>
@@ -2615,9 +1999,6 @@
         <v>36892</v>
       </c>
       <c r="B206" t="n">
-        <v>0.647924731182796</v>
-      </c>
-      <c r="C206" t="n">
         <v>8.31759543010753</v>
       </c>
     </row>
@@ -2626,9 +2007,6 @@
         <v>36923</v>
       </c>
       <c r="B207" t="n">
-        <v>0.520263392857143</v>
-      </c>
-      <c r="C207" t="n">
         <v>7.35085714285714</v>
       </c>
     </row>
@@ -2637,9 +2015,6 @@
         <v>36951</v>
       </c>
       <c r="B208" t="n">
-        <v>0.456002688172043</v>
-      </c>
-      <c r="C208" t="n">
         <v>6.91549193548387</v>
       </c>
     </row>
@@ -2648,9 +2023,6 @@
         <v>36982</v>
       </c>
       <c r="B209" t="n">
-        <v>0.553613888888889</v>
-      </c>
-      <c r="C209" t="n">
         <v>7.65129861111111</v>
       </c>
     </row>
@@ -2659,9 +2031,6 @@
         <v>37012</v>
       </c>
       <c r="B210" t="n">
-        <v>0.521161290322581</v>
-      </c>
-      <c r="C210" t="n">
         <v>7.35501209677419</v>
       </c>
     </row>
@@ -2670,9 +2039,6 @@
         <v>37043</v>
       </c>
       <c r="B211" t="n">
-        <v>0.682909722222222</v>
-      </c>
-      <c r="C211" t="n">
         <v>8.60189583333333</v>
       </c>
     </row>
@@ -2681,9 +2047,6 @@
         <v>37073</v>
       </c>
       <c r="B212" t="n">
-        <v>0.715008064516129</v>
-      </c>
-      <c r="C212" t="n">
         <v>8.859375</v>
       </c>
     </row>
@@ -2692,9 +2055,6 @@
         <v>37104</v>
       </c>
       <c r="B213" t="n">
-        <v>0.810412634408602</v>
-      </c>
-      <c r="C213" t="n">
         <v>9.80549865591398</v>
       </c>
     </row>
@@ -2703,9 +2063,6 @@
         <v>37135</v>
       </c>
       <c r="B214" t="n">
-        <v>0.709913888888889</v>
-      </c>
-      <c r="C214" t="n">
         <v>8.84597777777778</v>
       </c>
     </row>
@@ -2714,9 +2071,6 @@
         <v>37165</v>
       </c>
       <c r="B215" t="n">
-        <v>0.622539703903096</v>
-      </c>
-      <c r="C215" t="n">
         <v>8.09554912516824</v>
       </c>
     </row>
@@ -2725,9 +2079,6 @@
         <v>37196</v>
       </c>
       <c r="B216" t="n">
-        <v>0.629895833333333</v>
-      </c>
-      <c r="C216" t="n">
         <v>8.11742361111111</v>
       </c>
     </row>
@@ -2736,9 +2087,6 @@
         <v>37226</v>
       </c>
       <c r="B217" t="n">
-        <v>0.699966397849462</v>
-      </c>
-      <c r="C217" t="n">
         <v>8.73571774193548</v>
       </c>
     </row>
@@ -2747,9 +2095,6 @@
         <v>37257</v>
       </c>
       <c r="B218" t="n">
-        <v>0.478646505376344</v>
-      </c>
-      <c r="C218" t="n">
         <v>7.06585080645161</v>
       </c>
     </row>
@@ -2758,9 +2103,6 @@
         <v>37288</v>
       </c>
       <c r="B219" t="n">
-        <v>0.558471726190476</v>
-      </c>
-      <c r="C219" t="n">
         <v>7.63298511904762</v>
       </c>
     </row>
@@ -2769,9 +2111,6 @@
         <v>37316</v>
       </c>
       <c r="B220" t="n">
-        <v>0.51766935483871</v>
-      </c>
-      <c r="C220" t="n">
         <v>7.32455107526882</v>
       </c>
     </row>
@@ -2780,9 +2119,6 @@
         <v>37347</v>
       </c>
       <c r="B221" t="n">
-        <v>0.554176388888889</v>
-      </c>
-      <c r="C221" t="n">
         <v>7.56181388888889</v>
       </c>
     </row>
@@ -2791,9 +2127,6 @@
         <v>37377</v>
       </c>
       <c r="B222" t="n">
-        <v>0.596495967741935</v>
-      </c>
-      <c r="C222" t="n">
         <v>7.91838037634409</v>
       </c>
     </row>
@@ -2802,9 +2135,6 @@
         <v>37408</v>
       </c>
       <c r="B223" t="n">
-        <v>0.657801388888889</v>
-      </c>
-      <c r="C223" t="n">
         <v>8.36969305555556</v>
       </c>
     </row>
@@ -2813,9 +2143,6 @@
         <v>37438</v>
       </c>
       <c r="B224" t="n">
-        <v>0.657239247311828</v>
-      </c>
-      <c r="C224" t="n">
         <v>8.39451747311828</v>
       </c>
     </row>
@@ -2824,9 +2151,6 @@
         <v>37469</v>
       </c>
       <c r="B225" t="n">
-        <v>0.784942204301075</v>
-      </c>
-      <c r="C225" t="n">
         <v>9.61986827956989</v>
       </c>
     </row>
@@ -2835,9 +2159,6 @@
         <v>37500</v>
       </c>
       <c r="B226" t="n">
-        <v>0.699601388888889</v>
-      </c>
-      <c r="C226" t="n">
         <v>8.74364027777778</v>
       </c>
     </row>
@@ -2846,9 +2167,6 @@
         <v>37530</v>
       </c>
       <c r="B227" t="n">
-        <v>0.764545698924731</v>
-      </c>
-      <c r="C227" t="n">
         <v>9.33659946236559</v>
       </c>
     </row>
@@ -2857,9 +2175,6 @@
         <v>37561</v>
       </c>
       <c r="B228" t="n">
-        <v>0.671652294853964</v>
-      </c>
-      <c r="C228" t="n">
         <v>8.46897913769124</v>
       </c>
     </row>
@@ -2868,9 +2183,6 @@
         <v>37591</v>
       </c>
       <c r="B229" t="n">
-        <v>0.572787634408602</v>
-      </c>
-      <c r="C229" t="n">
         <v>7.74077956989247</v>
       </c>
     </row>
@@ -2879,9 +2191,6 @@
         <v>37622</v>
       </c>
       <c r="B230" t="n">
-        <v>0.399775537634409</v>
-      </c>
-      <c r="C230" t="n">
         <v>6.48687096774194</v>
       </c>
     </row>
@@ -2890,9 +2199,6 @@
         <v>37653</v>
       </c>
       <c r="B231" t="n">
-        <v>0.5351875</v>
-      </c>
-      <c r="C231" t="n">
         <v>7.50139732142857</v>
       </c>
     </row>
@@ -2901,9 +2207,6 @@
         <v>37681</v>
       </c>
       <c r="B232" t="n">
-        <v>0.434817204301075</v>
-      </c>
-      <c r="C232" t="n">
         <v>6.72985349462366</v>
       </c>
     </row>
@@ -2912,9 +2215,6 @@
         <v>37712</v>
       </c>
       <c r="B233" t="n">
-        <v>0.477995833333333</v>
-      </c>
-      <c r="C233" t="n">
         <v>7.03195555555556</v>
       </c>
     </row>
@@ -2923,9 +2223,6 @@
         <v>37742</v>
       </c>
       <c r="B234" t="n">
-        <v>0.532942204301075</v>
-      </c>
-      <c r="C234" t="n">
         <v>7.44304435483871</v>
       </c>
     </row>
@@ -2934,9 +2231,6 @@
         <v>37773</v>
       </c>
       <c r="B235" t="n">
-        <v>0.654940277777778</v>
-      </c>
-      <c r="C235" t="n">
         <v>8.34328194444444</v>
       </c>
     </row>
@@ -2945,9 +2239,6 @@
         <v>37803</v>
       </c>
       <c r="B236" t="n">
-        <v>0.744743279569893</v>
-      </c>
-      <c r="C236" t="n">
         <v>9.21813978494624</v>
       </c>
     </row>
@@ -2956,9 +2247,6 @@
         <v>37834</v>
       </c>
       <c r="B237" t="n">
-        <v>0.700565860215054</v>
-      </c>
-      <c r="C237" t="n">
         <v>8.73647311827957</v>
       </c>
     </row>
@@ -2967,9 +2255,6 @@
         <v>37865</v>
       </c>
       <c r="B238" t="n">
-        <v>0.764016666666667</v>
-      </c>
-      <c r="C238" t="n">
         <v>9.35914027777778</v>
       </c>
     </row>
@@ -2978,9 +2263,6 @@
         <v>37895</v>
       </c>
       <c r="B239" t="n">
-        <v>0.744803499327052</v>
-      </c>
-      <c r="C239" t="n">
         <v>9.12359219380888</v>
       </c>
     </row>
@@ -2989,9 +2271,6 @@
         <v>37926</v>
       </c>
       <c r="B240" t="n">
-        <v>0.659102777777778</v>
-      </c>
-      <c r="C240" t="n">
         <v>8.39738194444444</v>
       </c>
     </row>
@@ -3000,9 +2279,6 @@
         <v>37956</v>
       </c>
       <c r="B241" t="n">
-        <v>0.64092876344086</v>
-      </c>
-      <c r="C241" t="n">
         <v>8.2472002688172</v>
       </c>
     </row>
@@ -3011,9 +2287,6 @@
         <v>37987</v>
       </c>
       <c r="B242" t="n">
-        <v>0.39932123655914</v>
-      </c>
-      <c r="C242" t="n">
         <v>6.4232123655914</v>
       </c>
     </row>
@@ -3022,9 +2295,6 @@
         <v>38018</v>
       </c>
       <c r="B243" t="n">
-        <v>0.510817528735632</v>
-      </c>
-      <c r="C243" t="n">
         <v>7.2761091954023</v>
       </c>
     </row>
@@ -3033,9 +2303,6 @@
         <v>38047</v>
       </c>
       <c r="B244" t="n">
-        <v>0.584327956989247</v>
-      </c>
-      <c r="C244" t="n">
         <v>7.82779166666667</v>
       </c>
     </row>
@@ -3044,9 +2311,6 @@
         <v>38078</v>
       </c>
       <c r="B245" t="n">
-        <v>0.574136111111111</v>
-      </c>
-      <c r="C245" t="n">
         <v>7.73768888888889</v>
       </c>
     </row>
@@ -3055,9 +2319,6 @@
         <v>38108</v>
       </c>
       <c r="B246" t="n">
-        <v>0.543637096774194</v>
-      </c>
-      <c r="C246" t="n">
         <v>7.55349865591398</v>
       </c>
     </row>
@@ -3066,9 +2327,6 @@
         <v>38139</v>
       </c>
       <c r="B247" t="n">
-        <v>0.643704166666667</v>
-      </c>
-      <c r="C247" t="n">
         <v>8.29868055555556</v>
       </c>
     </row>
@@ -3077,9 +2335,6 @@
         <v>38169</v>
       </c>
       <c r="B248" t="n">
-        <v>0.657930107526882</v>
-      </c>
-      <c r="C248" t="n">
         <v>8.47234408602151</v>
       </c>
     </row>
@@ -3088,9 +2343,6 @@
         <v>38200</v>
       </c>
       <c r="B249" t="n">
-        <v>0.736481182795699</v>
-      </c>
-      <c r="C249" t="n">
         <v>9.10386962365591</v>
       </c>
     </row>
@@ -3099,9 +2351,6 @@
         <v>38231</v>
       </c>
       <c r="B250" t="n">
-        <v>0.798697222222222</v>
-      </c>
-      <c r="C250" t="n">
         <v>9.68214861111111</v>
       </c>
     </row>
@@ -3110,9 +2359,6 @@
         <v>38261</v>
       </c>
       <c r="B251" t="n">
-        <v>0.721311827956989</v>
-      </c>
-      <c r="C251" t="n">
         <v>8.89390860215054</v>
       </c>
     </row>
@@ -3121,9 +2367,6 @@
         <v>38292</v>
       </c>
       <c r="B252" t="n">
-        <v>0.690203059805285</v>
-      </c>
-      <c r="C252" t="n">
         <v>8.67019888734353</v>
       </c>
     </row>
@@ -3132,9 +2375,6 @@
         <v>38322</v>
       </c>
       <c r="B253" t="n">
-        <v>0.629411290322581</v>
-      </c>
-      <c r="C253" t="n">
         <v>8.14050268817204</v>
       </c>
     </row>
@@ -3143,9 +2383,6 @@
         <v>38353</v>
       </c>
       <c r="B254" t="n">
-        <v>0.515200268817204</v>
-      </c>
-      <c r="C254" t="n">
         <v>7.33492204301075</v>
       </c>
     </row>
@@ -3154,9 +2391,6 @@
         <v>38384</v>
       </c>
       <c r="B255" t="n">
-        <v>0.541377976190476</v>
-      </c>
-      <c r="C255" t="n">
         <v>7.54484077380952</v>
       </c>
     </row>
@@ -3165,9 +2399,6 @@
         <v>38412</v>
       </c>
       <c r="B256" t="n">
-        <v>0.432514784946237</v>
-      </c>
-      <c r="C256" t="n">
         <v>6.69116129032258</v>
       </c>
     </row>
@@ -3176,9 +2407,6 @@
         <v>38443</v>
       </c>
       <c r="B257" t="n">
-        <v>0.606438888888889</v>
-      </c>
-      <c r="C257" t="n">
         <v>8.00090277777778</v>
       </c>
     </row>
@@ -3187,9 +2415,6 @@
         <v>38473</v>
       </c>
       <c r="B258" t="n">
-        <v>0.594245967741935</v>
-      </c>
-      <c r="C258" t="n">
         <v>7.94511559139785</v>
       </c>
     </row>
@@ -3198,9 +2423,6 @@
         <v>38504</v>
       </c>
       <c r="B259" t="n">
-        <v>0.647316666666667</v>
-      </c>
-      <c r="C259" t="n">
         <v>8.38573333333333</v>
       </c>
     </row>
@@ -3209,9 +2431,6 @@
         <v>38534</v>
       </c>
       <c r="B260" t="n">
-        <v>0.697661290322581</v>
-      </c>
-      <c r="C260" t="n">
         <v>8.78011827956989</v>
       </c>
     </row>
@@ -3220,9 +2439,6 @@
         <v>38565</v>
       </c>
       <c r="B261" t="n">
-        <v>0.760908602150538</v>
-      </c>
-      <c r="C261" t="n">
         <v>9.24479032258064</v>
       </c>
     </row>
@@ -3231,9 +2447,6 @@
         <v>38596</v>
       </c>
       <c r="B262" t="n">
-        <v>0.723343055555556</v>
-      </c>
-      <c r="C262" t="n">
         <v>8.98830694444444</v>
       </c>
     </row>
@@ -3242,9 +2455,6 @@
         <v>38626</v>
       </c>
       <c r="B263" t="n">
-        <v>0.740257065948856</v>
-      </c>
-      <c r="C263" t="n">
         <v>9.13463795423957</v>
       </c>
     </row>
@@ -3253,9 +2463,6 @@
         <v>38657</v>
       </c>
       <c r="B264" t="n">
-        <v>0.695448611111111</v>
-      </c>
-      <c r="C264" t="n">
         <v>8.69712638888889</v>
       </c>
     </row>
@@ -3264,9 +2471,6 @@
         <v>38687</v>
       </c>
       <c r="B265" t="n">
-        <v>0.649174731182796</v>
-      </c>
-      <c r="C265" t="n">
         <v>8.35483602150538</v>
       </c>
     </row>
@@ -3275,9 +2479,6 @@
         <v>38718</v>
       </c>
       <c r="B266" t="n">
-        <v>0.714293010752688</v>
-      </c>
-      <c r="C266" t="n">
         <v>8.82877150537634</v>
       </c>
     </row>
@@ -3286,9 +2487,6 @@
         <v>38749</v>
       </c>
       <c r="B267" t="n">
-        <v>0.400105654761905</v>
-      </c>
-      <c r="C267" t="n">
         <v>6.51135565476191</v>
       </c>
     </row>
@@ -3297,9 +2495,6 @@
         <v>38777</v>
       </c>
       <c r="B268" t="n">
-        <v>0.413603494623656</v>
-      </c>
-      <c r="C268" t="n">
         <v>6.62346774193548</v>
       </c>
     </row>
@@ -3308,9 +2503,6 @@
         <v>38808</v>
       </c>
       <c r="B269" t="n">
-        <v>0.335319444444444</v>
-      </c>
-      <c r="C269" t="n">
         <v>5.99674305555556</v>
       </c>
     </row>
@@ -3319,9 +2511,6 @@
         <v>38838</v>
       </c>
       <c r="B270" t="n">
-        <v>0.543793010752688</v>
-      </c>
-      <c r="C270" t="n">
         <v>7.56802150537634</v>
       </c>
     </row>
@@ -3330,9 +2519,6 @@
         <v>38869</v>
       </c>
       <c r="B271" t="n">
-        <v>0.709170833333333</v>
-      </c>
-      <c r="C271" t="n">
         <v>8.96871944444444</v>
       </c>
     </row>
@@ -3341,9 +2527,6 @@
         <v>38899</v>
       </c>
       <c r="B272" t="n">
-        <v>0.715462365591398</v>
-      </c>
-      <c r="C272" t="n">
         <v>8.9909811827957</v>
       </c>
     </row>
@@ -3352,9 +2535,6 @@
         <v>38930</v>
       </c>
       <c r="B273" t="n">
-        <v>0.739986559139785</v>
-      </c>
-      <c r="C273" t="n">
         <v>9.17108467741935</v>
       </c>
     </row>
@@ -3363,9 +2543,6 @@
         <v>38961</v>
       </c>
       <c r="B274" t="n">
-        <v>0.718148611111111</v>
-      </c>
-      <c r="C274" t="n">
         <v>8.94165416666667</v>
       </c>
     </row>
@@ -3374,9 +2551,6 @@
         <v>38991</v>
       </c>
       <c r="B275" t="n">
-        <v>0.666724462365591</v>
-      </c>
-      <c r="C275" t="n">
         <v>8.47157661290323</v>
       </c>
     </row>
@@ -3385,9 +2559,6 @@
         <v>39022</v>
       </c>
       <c r="B276" t="n">
-        <v>0.649472878998609</v>
-      </c>
-      <c r="C276" t="n">
         <v>8.346578581363</v>
       </c>
     </row>
@@ -3396,9 +2567,6 @@
         <v>39052</v>
       </c>
       <c r="B277" t="n">
-        <v>0.565243279569893</v>
-      </c>
-      <c r="C277" t="n">
         <v>7.70520833333333</v>
       </c>
     </row>
@@ -3407,9 +2575,6 @@
         <v>39083</v>
       </c>
       <c r="B278" t="n">
-        <v>0.587301075268817</v>
-      </c>
-      <c r="C278" t="n">
         <v>7.83544623655914</v>
       </c>
     </row>
@@ -3418,9 +2583,6 @@
         <v>39114</v>
       </c>
       <c r="B279" t="n">
-        <v>0.434994047619048</v>
-      </c>
-      <c r="C279" t="n">
         <v>6.74958035714286</v>
       </c>
     </row>
@@ -3429,9 +2591,6 @@
         <v>39142</v>
       </c>
       <c r="B280" t="n">
-        <v>0.59989247311828</v>
-      </c>
-      <c r="C280" t="n">
         <v>7.97366532258065</v>
       </c>
     </row>
@@ -3440,9 +2599,6 @@
         <v>39173</v>
       </c>
       <c r="B281" t="n">
-        <v>0.500141666666667</v>
-      </c>
-      <c r="C281" t="n">
         <v>7.21206944444444</v>
       </c>
     </row>
@@ -3451,9 +2607,6 @@
         <v>39203</v>
       </c>
       <c r="B282" t="n">
-        <v>0.582688172043011</v>
-      </c>
-      <c r="C282" t="n">
         <v>7.8552123655914</v>
       </c>
     </row>
@@ -3462,9 +2615,6 @@
         <v>39234</v>
       </c>
       <c r="B283" t="n">
-        <v>0.6978125</v>
-      </c>
-      <c r="C283" t="n">
         <v>8.77629027777778</v>
       </c>
     </row>
@@ -3473,9 +2623,6 @@
         <v>39264</v>
       </c>
       <c r="B284" t="n">
-        <v>0.71257123655914</v>
-      </c>
-      <c r="C284" t="n">
         <v>8.88122580645161</v>
       </c>
     </row>
@@ -3484,9 +2631,6 @@
         <v>39295</v>
       </c>
       <c r="B285" t="n">
-        <v>0.818950268817204</v>
-      </c>
-      <c r="C285" t="n">
         <v>9.93258602150538</v>
       </c>
     </row>
@@ -3495,9 +2639,6 @@
         <v>39326</v>
       </c>
       <c r="B286" t="n">
-        <v>0.826584722222222</v>
-      </c>
-      <c r="C286" t="n">
         <v>10.1023777777778</v>
       </c>
     </row>
@@ -3506,9 +2647,6 @@
         <v>39356</v>
       </c>
       <c r="B287" t="n">
-        <v>0.757773889636608</v>
-      </c>
-      <c r="C287" t="n">
         <v>9.28819919246299</v>
       </c>
     </row>
@@ -3517,9 +2655,6 @@
         <v>39387</v>
       </c>
       <c r="B288" t="n">
-        <v>0.670670833333333</v>
-      </c>
-      <c r="C288" t="n">
         <v>8.55646388888889</v>
       </c>
     </row>
@@ -3528,9 +2663,6 @@
         <v>39417</v>
       </c>
       <c r="B289" t="n">
-        <v>0.656166666666667</v>
-      </c>
-      <c r="C289" t="n">
         <v>8.33858467741936</v>
       </c>
     </row>
@@ -3539,9 +2671,6 @@
         <v>39448</v>
       </c>
       <c r="B290" t="n">
-        <v>0.57722311827957</v>
-      </c>
-      <c r="C290" t="n">
         <v>7.79401075268817</v>
       </c>
     </row>
@@ -3550,9 +2679,6 @@
         <v>39479</v>
       </c>
       <c r="B291" t="n">
-        <v>0.498727011494253</v>
-      </c>
-      <c r="C291" t="n">
         <v>7.19588505747126</v>
       </c>
     </row>
@@ -3561,9 +2687,6 @@
         <v>39508</v>
       </c>
       <c r="B292" t="n">
-        <v>0.268481182795699</v>
-      </c>
-      <c r="C292" t="n">
         <v>5.44552016129032</v>
       </c>
     </row>
@@ -3572,9 +2695,6 @@
         <v>39539</v>
       </c>
       <c r="B293" t="n">
-        <v>0.36395</v>
-      </c>
-      <c r="C293" t="n">
         <v>6.11252083333333</v>
       </c>
     </row>
@@ -3583,9 +2703,6 @@
         <v>39569</v>
       </c>
       <c r="B294" t="n">
-        <v>0.474146505376344</v>
-      </c>
-      <c r="C294" t="n">
         <v>7.02932930107527</v>
       </c>
     </row>
@@ -3594,9 +2711,6 @@
         <v>39600</v>
       </c>
       <c r="B295" t="n">
-        <v>0.710695833333333</v>
-      </c>
-      <c r="C295" t="n">
         <v>8.94488611111111</v>
       </c>
     </row>
@@ -3605,9 +2719,6 @@
         <v>39630</v>
       </c>
       <c r="B296" t="n">
-        <v>0.781661290322581</v>
-      </c>
-      <c r="C296" t="n">
         <v>9.57973655913979</v>
       </c>
     </row>
@@ -3616,9 +2727,6 @@
         <v>39661</v>
       </c>
       <c r="B297" t="n">
-        <v>0.739248655913978</v>
-      </c>
-      <c r="C297" t="n">
         <v>9.1418561827957</v>
       </c>
     </row>
@@ -3627,9 +2735,6 @@
         <v>39692</v>
       </c>
       <c r="B298" t="n">
-        <v>0.767193055555556</v>
-      </c>
-      <c r="C298" t="n">
         <v>9.36669027777778</v>
       </c>
     </row>
@@ -3638,9 +2743,6 @@
         <v>39722</v>
       </c>
       <c r="B299" t="n">
-        <v>0.783884253028264</v>
-      </c>
-      <c r="C299" t="n">
         <v>9.67942395693136</v>
       </c>
     </row>
@@ -3649,9 +2751,6 @@
         <v>39753</v>
       </c>
       <c r="B300" t="n">
-        <v>0.662222222222222</v>
-      </c>
-      <c r="C300" t="n">
         <v>8.39740277777778</v>
       </c>
     </row>
@@ -3660,9 +2759,6 @@
         <v>39783</v>
       </c>
       <c r="B301" t="n">
-        <v>0.564771505376344</v>
-      </c>
-      <c r="C301" t="n">
         <v>7.66856317204301</v>
       </c>
     </row>
@@ -3671,9 +2767,6 @@
         <v>39814</v>
       </c>
       <c r="B302" t="n">
-        <v>0.51777688172043</v>
-      </c>
-      <c r="C302" t="n">
         <v>7.32232795698925</v>
       </c>
     </row>
@@ -3682,9 +2775,6 @@
         <v>39845</v>
       </c>
       <c r="B303" t="n">
-        <v>0.45153869047619</v>
-      </c>
-      <c r="C303" t="n">
         <v>6.85722172619048</v>
       </c>
     </row>
@@ -3693,9 +2783,6 @@
         <v>39873</v>
       </c>
       <c r="B304" t="n">
-        <v>0.367817204301075</v>
-      </c>
-      <c r="C304" t="n">
         <v>6.27802956989247</v>
       </c>
     </row>
@@ -3704,9 +2791,6 @@
         <v>39904</v>
       </c>
       <c r="B305" t="n">
-        <v>0.224411111111111</v>
-      </c>
-      <c r="C305" t="n">
         <v>4.93827361111111</v>
       </c>
     </row>
@@ -3715,9 +2799,6 @@
         <v>39934</v>
       </c>
       <c r="B306" t="n">
-        <v>0.298049731182796</v>
-      </c>
-      <c r="C306" t="n">
         <v>5.64777956989247</v>
       </c>
     </row>
@@ -3726,9 +2807,6 @@
         <v>39965</v>
       </c>
       <c r="B307" t="n">
-        <v>0.589802777777778</v>
-      </c>
-      <c r="C307" t="n">
         <v>7.88604722222222</v>
       </c>
     </row>
@@ -3737,9 +2815,6 @@
         <v>39995</v>
       </c>
       <c r="B308" t="n">
-        <v>0.629020161290323</v>
-      </c>
-      <c r="C308" t="n">
         <v>8.14571505376344</v>
       </c>
     </row>
@@ -3748,9 +2823,6 @@
         <v>40026</v>
       </c>
       <c r="B309" t="n">
-        <v>0.683029569892473</v>
-      </c>
-      <c r="C309" t="n">
         <v>8.59495295698925</v>
       </c>
     </row>
@@ -3759,9 +2831,6 @@
         <v>40057</v>
       </c>
       <c r="B310" t="n">
-        <v>0.680259722222222</v>
-      </c>
-      <c r="C310" t="n">
         <v>8.51521527777778</v>
       </c>
     </row>
@@ -3770,9 +2839,6 @@
         <v>40087</v>
       </c>
       <c r="B311" t="n">
-        <v>0.592312247644684</v>
-      </c>
-      <c r="C311" t="n">
         <v>7.82819246298789</v>
       </c>
     </row>
@@ -3781,9 +2847,6 @@
         <v>40118</v>
       </c>
       <c r="B312" t="n">
-        <v>0.676695833333333</v>
-      </c>
-      <c r="C312" t="n">
         <v>8.51219722222222</v>
       </c>
     </row>
@@ -3792,9 +2855,6 @@
         <v>40148</v>
       </c>
       <c r="B313" t="n">
-        <v>0.549990591397849</v>
-      </c>
-      <c r="C313" t="n">
         <v>7.58968010752688</v>
       </c>
     </row>
@@ -3803,9 +2863,6 @@
         <v>40179</v>
       </c>
       <c r="B314" t="n">
-        <v>0.450364247311828</v>
-      </c>
-      <c r="C314" t="n">
         <v>6.87276075268817</v>
       </c>
     </row>
@@ -3814,9 +2871,6 @@
         <v>40210</v>
       </c>
       <c r="B315" t="n">
-        <v>0.532815476190476</v>
-      </c>
-      <c r="C315" t="n">
         <v>7.47109821428571</v>
       </c>
     </row>
@@ -3825,9 +2879,6 @@
         <v>40238</v>
       </c>
       <c r="B316" t="n">
-        <v>0.398596774193548</v>
-      </c>
-      <c r="C316" t="n">
         <v>6.54288844086021</v>
       </c>
     </row>
@@ -3836,9 +2887,6 @@
         <v>40269</v>
       </c>
       <c r="B317" t="n">
-        <v>0.535402777777778</v>
-      </c>
-      <c r="C317" t="n">
         <v>7.43517777777778</v>
       </c>
     </row>
@@ -3847,9 +2895,6 @@
         <v>40299</v>
       </c>
       <c r="B318" t="n">
-        <v>0.530208333333333</v>
-      </c>
-      <c r="C318" t="n">
         <v>7.42170967741936</v>
       </c>
     </row>
@@ -3858,9 +2903,6 @@
         <v>40330</v>
       </c>
       <c r="B319" t="n">
-        <v>0.638869444444444</v>
-      </c>
-      <c r="C319" t="n">
         <v>8.30780138888889</v>
       </c>
     </row>
@@ -3869,9 +2911,6 @@
         <v>40360</v>
       </c>
       <c r="B320" t="n">
-        <v>0.748434139784946</v>
-      </c>
-      <c r="C320" t="n">
         <v>9.32372849462366</v>
       </c>
     </row>
@@ -3880,9 +2919,6 @@
         <v>40391</v>
       </c>
       <c r="B321" t="n">
-        <v>0.790641129032258</v>
-      </c>
-      <c r="C321" t="n">
         <v>9.71375403225806</v>
       </c>
     </row>
@@ -3891,9 +2927,6 @@
         <v>40422</v>
       </c>
       <c r="B322" t="n">
-        <v>0.806775</v>
-      </c>
-      <c r="C322" t="n">
         <v>9.85872222222222</v>
       </c>
     </row>
@@ -3902,9 +2935,6 @@
         <v>40452</v>
       </c>
       <c r="B323" t="n">
-        <v>0.59371736204576</v>
-      </c>
-      <c r="C323" t="n">
         <v>7.9934401076716</v>
       </c>
     </row>
@@ -3913,9 +2943,6 @@
         <v>40483</v>
       </c>
       <c r="B324" t="n">
-        <v>0.675423611111111</v>
-      </c>
-      <c r="C324" t="n">
         <v>8.53367777777778</v>
       </c>
     </row>
@@ -3924,9 +2951,6 @@
         <v>40513</v>
       </c>
       <c r="B325" t="n">
-        <v>0.55915188172043</v>
-      </c>
-      <c r="C325" t="n">
         <v>7.67507392473118</v>
       </c>
     </row>
@@ -3935,9 +2959,6 @@
         <v>40544</v>
       </c>
       <c r="B326" t="n">
-        <v>0.44802688172043</v>
-      </c>
-      <c r="C326" t="n">
         <v>6.79988440860215</v>
       </c>
     </row>
@@ -3946,9 +2967,6 @@
         <v>40575</v>
       </c>
       <c r="B327" t="n">
-        <v>0.501026785714286</v>
-      </c>
-      <c r="C327" t="n">
         <v>7.22609226190476</v>
       </c>
     </row>
@@ -3957,9 +2975,6 @@
         <v>40603</v>
       </c>
       <c r="B328" t="n">
-        <v>0.340672043010753</v>
-      </c>
-      <c r="C328" t="n">
         <v>6.01138440860215</v>
       </c>
     </row>
@@ -3968,9 +2983,6 @@
         <v>40634</v>
       </c>
       <c r="B329" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="C329" t="n">
         <v>6.83093333333333</v>
       </c>
     </row>
@@ -3979,9 +2991,6 @@
         <v>40664</v>
       </c>
       <c r="B330" t="n">
-        <v>0.574443548387097</v>
-      </c>
-      <c r="C330" t="n">
         <v>7.78873521505376</v>
       </c>
     </row>
@@ -3990,9 +2999,6 @@
         <v>40695</v>
       </c>
       <c r="B331" t="n">
-        <v>0.6349125</v>
-      </c>
-      <c r="C331" t="n">
         <v>8.21390138888889</v>
       </c>
     </row>
@@ -4001,9 +3007,6 @@
         <v>40725</v>
       </c>
       <c r="B332" t="n">
-        <v>0.692717741935484</v>
-      </c>
-      <c r="C332" t="n">
         <v>8.80127284946237</v>
       </c>
     </row>
@@ -4012,9 +3015,6 @@
         <v>40756</v>
       </c>
       <c r="B333" t="n">
-        <v>0.716340053763441</v>
-      </c>
-      <c r="C333" t="n">
         <v>8.88631451612903</v>
       </c>
     </row>
@@ -4023,9 +3023,6 @@
         <v>40787</v>
       </c>
       <c r="B334" t="n">
-        <v>0.811194444444444</v>
-      </c>
-      <c r="C334" t="n">
         <v>9.83890138888889</v>
       </c>
     </row>
@@ -4034,9 +3031,6 @@
         <v>40817</v>
       </c>
       <c r="B335" t="n">
-        <v>0.64671601615074</v>
-      </c>
-      <c r="C335" t="n">
         <v>8.29687213997308</v>
       </c>
     </row>
@@ -4045,9 +3039,6 @@
         <v>40848</v>
       </c>
       <c r="B336" t="n">
-        <v>0.666140277777778</v>
-      </c>
-      <c r="C336" t="n">
         <v>8.42114861111111</v>
       </c>
     </row>
@@ -4056,9 +3047,6 @@
         <v>40878</v>
       </c>
       <c r="B337" t="n">
-        <v>0.658313172043011</v>
-      </c>
-      <c r="C337" t="n">
         <v>8.3450376344086</v>
       </c>
     </row>
@@ -4067,9 +3055,6 @@
         <v>40909</v>
       </c>
       <c r="B338" t="n">
-        <v>0.626545698924731</v>
-      </c>
-      <c r="C338" t="n">
         <v>8.13804973118279</v>
       </c>
     </row>
@@ -4078,9 +3063,6 @@
         <v>40940</v>
       </c>
       <c r="B339" t="n">
-        <v>0.613968390804598</v>
-      </c>
-      <c r="C339" t="n">
         <v>8.07652298850575</v>
       </c>
     </row>
@@ -4089,9 +3071,6 @@
         <v>40969</v>
       </c>
       <c r="B340" t="n">
-        <v>0.628994623655914</v>
-      </c>
-      <c r="C340" t="n">
         <v>8.13044220430108</v>
       </c>
     </row>
@@ -4100,9 +3079,6 @@
         <v>41000</v>
       </c>
       <c r="B341" t="n">
-        <v>0.610011111111111</v>
-      </c>
-      <c r="C341" t="n">
         <v>7.97475833333333</v>
       </c>
     </row>
@@ -4111,9 +3087,6 @@
         <v>41030</v>
       </c>
       <c r="B342" t="n">
-        <v>0.638111559139785</v>
-      </c>
-      <c r="C342" t="n">
         <v>8.24422311827957</v>
       </c>
     </row>
@@ -4122,9 +3095,6 @@
         <v>41061</v>
       </c>
       <c r="B343" t="n">
-        <v>0.653419444444444</v>
-      </c>
-      <c r="C343" t="n">
         <v>8.35161527777778</v>
       </c>
     </row>
@@ -4133,9 +3103,6 @@
         <v>41091</v>
       </c>
       <c r="B344" t="n">
-        <v>0.73265188172043</v>
-      </c>
-      <c r="C344" t="n">
         <v>9.01179838709677</v>
       </c>
     </row>
@@ -4144,9 +3111,6 @@
         <v>41122</v>
       </c>
       <c r="B345" t="n">
-        <v>0.802162634408602</v>
-      </c>
-      <c r="C345" t="n">
         <v>9.87251209677419</v>
       </c>
     </row>
@@ -4155,9 +3119,6 @@
         <v>41153</v>
       </c>
       <c r="B346" t="n">
-        <v>0.790334722222222</v>
-      </c>
-      <c r="C346" t="n">
         <v>9.59883194444444</v>
       </c>
     </row>
@@ -4166,9 +3127,6 @@
         <v>41183</v>
       </c>
       <c r="B347" t="n">
-        <v>0.782585464333782</v>
-      </c>
-      <c r="C347" t="n">
         <v>9.55303903095558</v>
       </c>
     </row>
@@ -4177,9 +3135,6 @@
         <v>41214</v>
       </c>
       <c r="B348" t="n">
-        <v>0.5921375</v>
-      </c>
-      <c r="C348" t="n">
         <v>7.84367916666667</v>
       </c>
     </row>
@@ -4188,9 +3143,6 @@
         <v>41244</v>
       </c>
       <c r="B349" t="n">
-        <v>0.626319892473118</v>
-      </c>
-      <c r="C349" t="n">
         <v>8.09076747311828</v>
       </c>
     </row>
@@ -4199,9 +3151,6 @@
         <v>41275</v>
       </c>
       <c r="B350" t="n">
-        <v>0.58939247311828</v>
-      </c>
-      <c r="C350" t="n">
         <v>7.86550403225806</v>
       </c>
     </row>
@@ -4210,9 +3159,6 @@
         <v>41306</v>
       </c>
       <c r="B351" t="n">
-        <v>0.69136755952381</v>
-      </c>
-      <c r="C351" t="n">
         <v>8.62555803571429</v>
       </c>
     </row>
@@ -4221,9 +3167,6 @@
         <v>41334</v>
       </c>
       <c r="B352" t="n">
-        <v>0.545676075268817</v>
-      </c>
-      <c r="C352" t="n">
         <v>7.58910887096774</v>
       </c>
     </row>
@@ -4232,9 +3175,6 @@
         <v>41365</v>
       </c>
       <c r="B353" t="n">
-        <v>0.477434722222222</v>
-      </c>
-      <c r="C353" t="n">
         <v>7.02336944444444</v>
       </c>
     </row>
@@ -4243,9 +3183,6 @@
         <v>41395</v>
       </c>
       <c r="B354" t="n">
-        <v>0.56414247311828</v>
-      </c>
-      <c r="C354" t="n">
         <v>7.66264112903226</v>
       </c>
     </row>
@@ -4254,9 +3191,6 @@
         <v>41426</v>
       </c>
       <c r="B355" t="n">
-        <v>0.592352777777778</v>
-      </c>
-      <c r="C355" t="n">
         <v>7.8740625</v>
       </c>
     </row>
@@ -4265,9 +3199,6 @@
         <v>41456</v>
       </c>
       <c r="B356" t="n">
-        <v>0.632876344086022</v>
-      </c>
-      <c r="C356" t="n">
         <v>8.25986290322581</v>
       </c>
     </row>
@@ -4276,9 +3207,6 @@
         <v>41487</v>
       </c>
       <c r="B357" t="n">
-        <v>0.735516129032258</v>
-      </c>
-      <c r="C357" t="n">
         <v>9.02240994623656</v>
       </c>
     </row>
@@ -4287,9 +3215,6 @@
         <v>41518</v>
       </c>
       <c r="B358" t="n">
-        <v>0.761636111111111</v>
-      </c>
-      <c r="C358" t="n">
         <v>9.29066527777778</v>
       </c>
     </row>
@@ -4298,9 +3223,6 @@
         <v>41548</v>
       </c>
       <c r="B359" t="n">
-        <v>0.710621803499327</v>
-      </c>
-      <c r="C359" t="n">
         <v>8.79292866756393</v>
       </c>
     </row>
@@ -4309,9 +3231,6 @@
         <v>41579</v>
       </c>
       <c r="B360" t="n">
-        <v>0.685886111111111</v>
-      </c>
-      <c r="C360" t="n">
         <v>8.59244861111111</v>
       </c>
     </row>
@@ -4320,9 +3239,6 @@
         <v>41609</v>
       </c>
       <c r="B361" t="n">
-        <v>0.590573924731183</v>
-      </c>
-      <c r="C361" t="n">
         <v>7.84145698924731</v>
       </c>
     </row>
@@ -4331,9 +3247,6 @@
         <v>41640</v>
       </c>
       <c r="B362" t="n">
-        <v>0.654061827956989</v>
-      </c>
-      <c r="C362" t="n">
         <v>8.32679301075269</v>
       </c>
     </row>
@@ -4342,9 +3255,6 @@
         <v>41671</v>
       </c>
       <c r="B363" t="n">
-        <v>0.560720238095238</v>
-      </c>
-      <c r="C363" t="n">
         <v>7.62609375</v>
       </c>
     </row>
@@ -4353,9 +3263,6 @@
         <v>41699</v>
       </c>
       <c r="B364" t="n">
-        <v>0.50826747311828</v>
-      </c>
-      <c r="C364" t="n">
         <v>7.25739112903226</v>
       </c>
     </row>
@@ -4364,9 +3271,6 @@
         <v>41730</v>
       </c>
       <c r="B365" t="n">
-        <v>0.450598611111111</v>
-      </c>
-      <c r="C365" t="n">
         <v>6.83973611111111</v>
       </c>
     </row>
@@ -4375,9 +3279,6 @@
         <v>41760</v>
       </c>
       <c r="B366" t="n">
-        <v>0.557525537634409</v>
-      </c>
-      <c r="C366" t="n">
         <v>7.60192338709677</v>
       </c>
     </row>
@@ -4386,9 +3287,6 @@
         <v>41791</v>
       </c>
       <c r="B367" t="n">
-        <v>0.701334722222222</v>
-      </c>
-      <c r="C367" t="n">
         <v>8.75883611111111</v>
       </c>
     </row>
@@ -4397,9 +3295,6 @@
         <v>41821</v>
       </c>
       <c r="B368" t="n">
-        <v>0.724888440860215</v>
-      </c>
-      <c r="C368" t="n">
         <v>8.96202016129032</v>
       </c>
     </row>
@@ -4408,9 +3303,6 @@
         <v>41852</v>
       </c>
       <c r="B369" t="n">
-        <v>0.751426075268817</v>
-      </c>
-      <c r="C369" t="n">
         <v>9.19483467741935</v>
       </c>
     </row>
@@ -4419,9 +3311,6 @@
         <v>41883</v>
       </c>
       <c r="B370" t="n">
-        <v>0.706669444444444</v>
-      </c>
-      <c r="C370" t="n">
         <v>8.83669305555556</v>
       </c>
     </row>
@@ -4430,9 +3319,6 @@
         <v>41913</v>
       </c>
       <c r="B371" t="n">
-        <v>0.764672947510094</v>
-      </c>
-      <c r="C371" t="n">
         <v>9.40134724091521</v>
       </c>
     </row>
@@ -4441,9 +3327,6 @@
         <v>41944</v>
       </c>
       <c r="B372" t="n">
-        <v>0.614440277777778</v>
-      </c>
-      <c r="C372" t="n">
         <v>8.01106666666667</v>
       </c>
     </row>
@@ -4452,9 +3335,6 @@
         <v>41974</v>
       </c>
       <c r="B373" t="n">
-        <v>0.635711021505376</v>
-      </c>
-      <c r="C373" t="n">
         <v>8.22535887096774</v>
       </c>
     </row>
@@ -4463,9 +3343,6 @@
         <v>42005</v>
       </c>
       <c r="B374" t="n">
-        <v>0.646586021505376</v>
-      </c>
-      <c r="C374" t="n">
         <v>8.28743010752688</v>
       </c>
     </row>
@@ -4474,9 +3351,6 @@
         <v>42036</v>
       </c>
       <c r="B375" t="n">
-        <v>0.556168154761905</v>
-      </c>
-      <c r="C375" t="n">
         <v>7.61529761904762</v>
       </c>
     </row>
@@ -4485,9 +3359,6 @@
         <v>42064</v>
       </c>
       <c r="B376" t="n">
-        <v>0.502325268817204</v>
-      </c>
-      <c r="C376" t="n">
         <v>7.20021774193548</v>
       </c>
     </row>
@@ -4496,9 +3367,6 @@
         <v>42095</v>
       </c>
       <c r="B377" t="n">
-        <v>0.4364375</v>
-      </c>
-      <c r="C377" t="n">
         <v>6.74004305555556</v>
       </c>
     </row>
@@ -4507,9 +3375,6 @@
         <v>42125</v>
       </c>
       <c r="B378" t="n">
-        <v>0.603709677419355</v>
-      </c>
-      <c r="C378" t="n">
         <v>7.93450806451613</v>
       </c>
     </row>
@@ -4518,9 +3383,6 @@
         <v>42156</v>
       </c>
       <c r="B379" t="n">
-        <v>0.648429166666667</v>
-      </c>
-      <c r="C379" t="n">
         <v>8.33822638888889</v>
       </c>
     </row>
@@ -4529,9 +3391,6 @@
         <v>42186</v>
       </c>
       <c r="B380" t="n">
-        <v>0.726927419354839</v>
-      </c>
-      <c r="C380" t="n">
         <v>9.06674327956989</v>
       </c>
     </row>
@@ -4540,9 +3399,6 @@
         <v>42217</v>
       </c>
       <c r="B381" t="n">
-        <v>0.772708333333333</v>
-      </c>
-      <c r="C381" t="n">
         <v>9.45924462365591</v>
       </c>
     </row>
@@ -4551,9 +3407,6 @@
         <v>42248</v>
       </c>
       <c r="B382" t="n">
-        <v>0.707411111111111</v>
-      </c>
-      <c r="C382" t="n">
         <v>8.77005555555556</v>
       </c>
     </row>
@@ -4562,9 +3415,6 @@
         <v>42278</v>
       </c>
       <c r="B383" t="n">
-        <v>0.730191117092867</v>
-      </c>
-      <c r="C383" t="n">
         <v>9.03893943472409</v>
       </c>
     </row>
@@ -4573,9 +3423,6 @@
         <v>42309</v>
       </c>
       <c r="B384" t="n">
-        <v>0.610829166666667</v>
-      </c>
-      <c r="C384" t="n">
         <v>8.04113333333333</v>
       </c>
     </row>
@@ -4584,9 +3431,6 @@
         <v>42339</v>
       </c>
       <c r="B385" t="n">
-        <v>0.596342741935484</v>
-      </c>
-      <c r="C385" t="n">
         <v>7.90695161290323</v>
       </c>
     </row>
@@ -4595,9 +3439,6 @@
         <v>42370</v>
       </c>
       <c r="B386" t="n">
-        <v>0.389404569892473</v>
-      </c>
-      <c r="C386" t="n">
         <v>6.41842741935484</v>
       </c>
     </row>
@@ -4606,9 +3447,6 @@
         <v>42401</v>
       </c>
       <c r="B387" t="n">
-        <v>0.596399425287356</v>
-      </c>
-      <c r="C387" t="n">
         <v>7.88586781609195</v>
       </c>
     </row>
@@ -4617,9 +3455,6 @@
         <v>42430</v>
       </c>
       <c r="B388" t="n">
-        <v>0.557293010752688</v>
-      </c>
-      <c r="C388" t="n">
         <v>7.59444623655914</v>
       </c>
     </row>
@@ -4628,9 +3463,6 @@
         <v>42461</v>
       </c>
       <c r="B389" t="n">
-        <v>0.648111111111111</v>
-      </c>
-      <c r="C389" t="n">
         <v>8.33969722222222</v>
       </c>
     </row>
@@ -4639,9 +3471,6 @@
         <v>42491</v>
       </c>
       <c r="B390" t="n">
-        <v>0.548780913978495</v>
-      </c>
-      <c r="C390" t="n">
         <v>7.53223655913979</v>
       </c>
     </row>
@@ -4650,9 +3479,6 @@
         <v>42522</v>
       </c>
       <c r="B391" t="n">
-        <v>0.637448611111111</v>
-      </c>
-      <c r="C391" t="n">
         <v>8.31051805555555</v>
       </c>
     </row>
@@ -4661,9 +3487,6 @@
         <v>42552</v>
       </c>
       <c r="B392" t="n">
-        <v>0.740991935483871</v>
-      </c>
-      <c r="C392" t="n">
         <v>9.1504435483871</v>
       </c>
     </row>
@@ -4672,9 +3495,6 @@
         <v>42583</v>
       </c>
       <c r="B393" t="n">
-        <v>0.748610215053763</v>
-      </c>
-      <c r="C393" t="n">
         <v>9.15503897849462</v>
       </c>
     </row>
@@ -4683,9 +3503,6 @@
         <v>42614</v>
       </c>
       <c r="B394" t="n">
-        <v>0.7549625</v>
-      </c>
-      <c r="C394" t="n">
         <v>9.23952222222222</v>
       </c>
     </row>
@@ -4694,9 +3511,6 @@
         <v>42644</v>
       </c>
       <c r="B395" t="n">
-        <v>0.759037685060565</v>
-      </c>
-      <c r="C395" t="n">
         <v>9.38532436069987</v>
       </c>
     </row>
@@ -4705,9 +3519,6 @@
         <v>42675</v>
       </c>
       <c r="B396" t="n">
-        <v>0.718091666666667</v>
-      </c>
-      <c r="C396" t="n">
         <v>8.97898888888889</v>
       </c>
     </row>
@@ -4716,9 +3527,6 @@
         <v>42705</v>
       </c>
       <c r="B397" t="n">
-        <v>0.663611559139785</v>
-      </c>
-      <c r="C397" t="n">
         <v>8.43306182795699</v>
       </c>
     </row>
@@ -4727,9 +3535,6 @@
         <v>42736</v>
       </c>
       <c r="B398" t="n">
-        <v>0.635103494623656</v>
-      </c>
-      <c r="C398" t="n">
         <v>8.1692876344086</v>
       </c>
     </row>
@@ -4738,9 +3543,6 @@
         <v>42767</v>
       </c>
       <c r="B399" t="n">
-        <v>0.574797619047619</v>
-      </c>
-      <c r="C399" t="n">
         <v>7.71884226190476</v>
       </c>
     </row>
@@ -4749,9 +3551,6 @@
         <v>42795</v>
       </c>
       <c r="B400" t="n">
-        <v>0.484775537634409</v>
-      </c>
-      <c r="C400" t="n">
         <v>7.09971908602151</v>
       </c>
     </row>
@@ -4760,9 +3559,6 @@
         <v>42826</v>
       </c>
       <c r="B401" t="n">
-        <v>0.540775</v>
-      </c>
-      <c r="C401" t="n">
         <v>7.47974861111111</v>
       </c>
     </row>
@@ -4771,9 +3567,6 @@
         <v>42856</v>
       </c>
       <c r="B402" t="n">
-        <v>0.51145564516129</v>
-      </c>
-      <c r="C402" t="n">
         <v>7.2998185483871</v>
       </c>
     </row>
@@ -4782,9 +3575,6 @@
         <v>42887</v>
       </c>
       <c r="B403" t="n">
-        <v>0.681505555555556</v>
-      </c>
-      <c r="C403" t="n">
         <v>8.67084722222222</v>
       </c>
     </row>
@@ -4793,9 +3583,6 @@
         <v>42917</v>
       </c>
       <c r="B404" t="n">
-        <v>0.792025537634409</v>
-      </c>
-      <c r="C404" t="n">
         <v>9.97409946236559</v>
       </c>
     </row>
@@ -4804,9 +3591,6 @@
         <v>42948</v>
       </c>
       <c r="B405" t="n">
-        <v>0.740900537634409</v>
-      </c>
-      <c r="C405" t="n">
         <v>9.05605241935484</v>
       </c>
     </row>
@@ -4815,9 +3599,6 @@
         <v>42979</v>
       </c>
       <c r="B406" t="n">
-        <v>0.83575</v>
-      </c>
-      <c r="C406" t="n">
         <v>10.1541902777778</v>
       </c>
     </row>
@@ -4826,9 +3607,6 @@
         <v>43009</v>
       </c>
       <c r="B407" t="n">
-        <v>0.772419919246299</v>
-      </c>
-      <c r="C407" t="n">
         <v>9.4308869448183</v>
       </c>
     </row>
@@ -4837,9 +3615,6 @@
         <v>43040</v>
       </c>
       <c r="B408" t="n">
-        <v>0.6457875</v>
-      </c>
-      <c r="C408" t="n">
         <v>8.25638055555556</v>
       </c>
     </row>
@@ -4848,9 +3623,6 @@
         <v>43070</v>
       </c>
       <c r="B409" t="n">
-        <v>0.600619623655914</v>
-      </c>
-      <c r="C409" t="n">
         <v>7.91406586021505</v>
       </c>
     </row>
@@ -4859,9 +3631,6 @@
         <v>43101</v>
       </c>
       <c r="B410" t="n">
-        <v>0.558450268817204</v>
-      </c>
-      <c r="C410" t="n">
         <v>7.66092204301075</v>
       </c>
     </row>
@@ -4870,9 +3639,6 @@
         <v>43132</v>
       </c>
       <c r="B411" t="n">
-        <v>0.47011755952381</v>
-      </c>
-      <c r="C411" t="n">
         <v>7.00171577380952</v>
       </c>
     </row>
@@ -4881,9 +3647,6 @@
         <v>43160</v>
       </c>
       <c r="B412" t="n">
-        <v>0.415529569892473</v>
-      </c>
-      <c r="C412" t="n">
         <v>6.63204032258064</v>
       </c>
     </row>
@@ -4892,9 +3655,6 @@
         <v>43191</v>
       </c>
       <c r="B413" t="n">
-        <v>0.438395833333333</v>
-      </c>
-      <c r="C413" t="n">
         <v>6.65950416666667</v>
       </c>
     </row>
@@ -4903,9 +3663,6 @@
         <v>43221</v>
       </c>
       <c r="B414" t="n">
-        <v>0.603838709677419</v>
-      </c>
-      <c r="C414" t="n">
         <v>7.97067607526882</v>
       </c>
     </row>
@@ -4914,9 +3671,6 @@
         <v>43252</v>
       </c>
       <c r="B415" t="n">
-        <v>0.6819375</v>
-      </c>
-      <c r="C415" t="n">
         <v>8.57703472222222</v>
       </c>
     </row>
@@ -4925,9 +3679,6 @@
         <v>43282</v>
       </c>
       <c r="B416" t="n">
-        <v>0.750856182795699</v>
-      </c>
-      <c r="C416" t="n">
         <v>9.17409811827957</v>
       </c>
     </row>
@@ -4936,9 +3687,6 @@
         <v>43313</v>
       </c>
       <c r="B417" t="n">
-        <v>0.729208333333333</v>
-      </c>
-      <c r="C417" t="n">
         <v>8.99850403225807</v>
       </c>
     </row>
@@ -4947,9 +3695,6 @@
         <v>43344</v>
       </c>
       <c r="B418" t="n">
-        <v>0.768854166666667</v>
-      </c>
-      <c r="C418" t="n">
         <v>9.37242361111111</v>
       </c>
     </row>
@@ -4958,9 +3703,6 @@
         <v>43374</v>
       </c>
       <c r="B419" t="n">
-        <v>0.653116935483871</v>
-      </c>
-      <c r="C419" t="n">
         <v>8.36806048387097</v>
       </c>
     </row>
@@ -4969,9 +3711,6 @@
         <v>43405</v>
       </c>
       <c r="B420" t="n">
-        <v>0.725550764951321</v>
-      </c>
-      <c r="C420" t="n">
         <v>8.9320083449235</v>
       </c>
     </row>
@@ -4980,9 +3719,6 @@
         <v>43435</v>
       </c>
       <c r="B421" t="n">
-        <v>0.574524193548387</v>
-      </c>
-      <c r="C421" t="n">
         <v>7.78475672043011</v>
       </c>
     </row>
@@ -4991,9 +3727,6 @@
         <v>43466</v>
       </c>
       <c r="B422" t="n">
-        <v>0.588350806451613</v>
-      </c>
-      <c r="C422" t="n">
         <v>7.86048521505376</v>
       </c>
     </row>
@@ -5002,9 +3735,6 @@
         <v>43497</v>
       </c>
       <c r="B423" t="n">
-        <v>0.403008928571429</v>
-      </c>
-      <c r="C423" t="n">
         <v>6.49328869047619</v>
       </c>
     </row>
@@ -5013,9 +3743,6 @@
         <v>43525</v>
       </c>
       <c r="B424" t="n">
-        <v>0.37080376344086</v>
-      </c>
-      <c r="C424" t="n">
         <v>6.2323185483871</v>
       </c>
     </row>
@@ -5024,9 +3751,6 @@
         <v>43556</v>
       </c>
       <c r="B425" t="n">
-        <v>0.358347222222222</v>
-      </c>
-      <c r="C425" t="n">
         <v>6.140475</v>
       </c>
     </row>
@@ -5035,9 +3759,6 @@
         <v>43586</v>
       </c>
       <c r="B426" t="n">
-        <v>0.541237903225806</v>
-      </c>
-      <c r="C426" t="n">
         <v>7.48629704301075</v>
       </c>
     </row>
@@ -5046,9 +3767,6 @@
         <v>43617</v>
       </c>
       <c r="B427" t="n">
-        <v>0.692483333333333</v>
-      </c>
-      <c r="C427" t="n">
         <v>8.68562638888889</v>
       </c>
     </row>
@@ -5057,9 +3775,6 @@
         <v>43647</v>
       </c>
       <c r="B428" t="n">
-        <v>0.64719623655914</v>
-      </c>
-      <c r="C428" t="n">
         <v>8.34030913978495</v>
       </c>
     </row>
@@ -5068,9 +3783,6 @@
         <v>43678</v>
       </c>
       <c r="B429" t="n">
-        <v>0.781336021505376</v>
-      </c>
-      <c r="C429" t="n">
         <v>9.46143279569892</v>
       </c>
     </row>
@@ -5079,9 +3791,6 @@
         <v>43709</v>
       </c>
       <c r="B430" t="n">
-        <v>0.748501388888889</v>
-      </c>
-      <c r="C430" t="n">
         <v>9.13870138888889</v>
       </c>
     </row>
@@ -5090,9 +3799,6 @@
         <v>43739</v>
       </c>
       <c r="B431" t="n">
-        <v>0.71673252688172</v>
-      </c>
-      <c r="C431" t="n">
         <v>8.96122311827957</v>
       </c>
     </row>
@@ -5101,9 +3807,6 @@
         <v>43770</v>
       </c>
       <c r="B432" t="n">
-        <v>0.642827777777778</v>
-      </c>
-      <c r="C432" t="n">
         <v>8.24937361111111</v>
       </c>
     </row>
@@ -5112,9 +3815,6 @@
         <v>43800</v>
       </c>
       <c r="B433" t="n">
-        <v>0.603841397849462</v>
-      </c>
-      <c r="C433" t="n">
         <v>8.01029838709677</v>
       </c>
     </row>
@@ -5123,9 +3823,6 @@
         <v>43831</v>
       </c>
       <c r="B434" t="n">
-        <v>0.430745967741935</v>
-      </c>
-      <c r="C434" t="n">
         <v>6.73418413978495</v>
       </c>
     </row>
@@ -5134,9 +3831,6 @@
         <v>43862</v>
       </c>
       <c r="B435" t="n">
-        <v>0.433283045977012</v>
-      </c>
-      <c r="C435" t="n">
         <v>6.72138505747126</v>
       </c>
     </row>
@@ -5145,9 +3839,6 @@
         <v>43891</v>
       </c>
       <c r="B436" t="n">
-        <v>0.286573924731183</v>
-      </c>
-      <c r="C436" t="n">
         <v>5.57530376344086</v>
       </c>
     </row>
@@ -5156,9 +3847,6 @@
         <v>43922</v>
       </c>
       <c r="B437" t="n">
-        <v>0.382466666666667</v>
-      </c>
-      <c r="C437" t="n">
         <v>6.28510833333333</v>
       </c>
     </row>
@@ -5167,9 +3855,6 @@
         <v>43952</v>
       </c>
       <c r="B438" t="n">
-        <v>0.511307795698925</v>
-      </c>
-      <c r="C438" t="n">
         <v>7.24855510752688</v>
       </c>
     </row>
@@ -5178,9 +3863,6 @@
         <v>43983</v>
       </c>
       <c r="B439" t="n">
-        <v>0.651919444444444</v>
-      </c>
-      <c r="C439" t="n">
         <v>8.41915277777778</v>
       </c>
     </row>
@@ -5189,9 +3871,6 @@
         <v>44013</v>
       </c>
       <c r="B440" t="n">
-        <v>0.67860752688172</v>
-      </c>
-      <c r="C440" t="n">
         <v>8.58130913978495</v>
       </c>
     </row>
@@ -5200,9 +3879,6 @@
         <v>44044</v>
       </c>
       <c r="B441" t="n">
-        <v>0.770190860215054</v>
-      </c>
-      <c r="C441" t="n">
         <v>9.37095161290323</v>
       </c>
     </row>
@@ -5211,9 +3887,6 @@
         <v>44075</v>
       </c>
       <c r="B442" t="n">
-        <v>0.739445833333333</v>
-      </c>
-      <c r="C442" t="n">
         <v>9.01511527777778</v>
       </c>
     </row>
@@ -5222,9 +3895,6 @@
         <v>44105</v>
       </c>
       <c r="B443" t="n">
-        <v>0.627139784946237</v>
-      </c>
-      <c r="C443" t="n">
         <v>8.16303360215054</v>
       </c>
     </row>
@@ -5233,9 +3903,6 @@
         <v>44136</v>
       </c>
       <c r="B444" t="n">
-        <v>0.610918055555556</v>
-      </c>
-      <c r="C444" t="n">
         <v>8.063575</v>
       </c>
     </row>
@@ -5244,9 +3911,6 @@
         <v>44166</v>
       </c>
       <c r="B445" t="n">
-        <v>0.644298788694482</v>
-      </c>
-      <c r="C445" t="n">
         <v>8.25871601615074</v>
       </c>
     </row>
@@ -5255,9 +3919,6 @@
         <v>44197</v>
       </c>
       <c r="B446" t="n">
-        <v>0.552799731182796</v>
-      </c>
-      <c r="C446" t="n">
         <v>7.55119086021505</v>
       </c>
     </row>
@@ -5266,9 +3927,6 @@
         <v>44228</v>
       </c>
       <c r="B447" t="n">
-        <v>0.452688988095238</v>
-      </c>
-      <c r="C447" t="n">
         <v>6.88699255952381</v>
       </c>
     </row>
@@ -5277,9 +3935,6 @@
         <v>44256</v>
       </c>
       <c r="B448" t="n">
-        <v>0.468407258064516</v>
-      </c>
-      <c r="C448" t="n">
         <v>6.96209543010753</v>
       </c>
     </row>
@@ -5288,9 +3943,6 @@
         <v>44287</v>
       </c>
       <c r="B449" t="n">
-        <v>0.476136111111111</v>
-      </c>
-      <c r="C449" t="n">
         <v>7.05495555555556</v>
       </c>
     </row>
@@ -5299,9 +3951,6 @@
         <v>44317</v>
       </c>
       <c r="B450" t="n">
-        <v>0.548322580645161</v>
-      </c>
-      <c r="C450" t="n">
         <v>7.55805510752688</v>
       </c>
     </row>
@@ -5310,9 +3959,6 @@
         <v>44348</v>
       </c>
       <c r="B451" t="n">
-        <v>0.587001388888889</v>
-      </c>
-      <c r="C451" t="n">
         <v>7.82960972222222</v>
       </c>
     </row>
@@ -5321,9 +3967,6 @@
         <v>44378</v>
       </c>
       <c r="B452" t="n">
-        <v>0.655111559139785</v>
-      </c>
-      <c r="C452" t="n">
         <v>8.39078360215054</v>
       </c>
     </row>
@@ -5332,9 +3975,6 @@
         <v>44409</v>
       </c>
       <c r="B453" t="n">
-        <v>0.783659946236559</v>
-      </c>
-      <c r="C453" t="n">
         <v>9.56429569892473</v>
       </c>
     </row>
@@ -5343,9 +3983,6 @@
         <v>44440</v>
       </c>
       <c r="B454" t="n">
-        <v>0.709580555555556</v>
-      </c>
-      <c r="C454" t="n">
         <v>8.83671666666667</v>
       </c>
     </row>
@@ -5354,9 +3991,6 @@
         <v>44470</v>
       </c>
       <c r="B455" t="n">
-        <v>0.641948924731183</v>
-      </c>
-      <c r="C455" t="n">
         <v>8.26374193548387</v>
       </c>
     </row>
@@ -5365,9 +3999,6 @@
         <v>44501</v>
       </c>
       <c r="B456" t="n">
-        <v>0.567963888888889</v>
-      </c>
-      <c r="C456" t="n">
         <v>7.70726388888889</v>
       </c>
     </row>
@@ -5376,9 +4007,6 @@
         <v>44531</v>
       </c>
       <c r="B457" t="n">
-        <v>0.562176075268817</v>
-      </c>
-      <c r="C457" t="n">
         <v>7.68324193548387</v>
       </c>
     </row>
@@ -5387,9 +4015,6 @@
         <v>44562</v>
       </c>
       <c r="B458" t="n">
-        <v>0.429305107526882</v>
-      </c>
-      <c r="C458" t="n">
         <v>6.69292607526882</v>
       </c>
     </row>
@@ -5398,9 +4023,6 @@
         <v>44593</v>
       </c>
       <c r="B459" t="n">
-        <v>0.490956845238095</v>
-      </c>
-      <c r="C459" t="n">
         <v>7.13505803571429</v>
       </c>
     </row>
@@ -5409,9 +4031,6 @@
         <v>44621</v>
       </c>
       <c r="B460" t="n">
-        <v>0.424255376344086</v>
-      </c>
-      <c r="C460" t="n">
         <v>6.65203225806452</v>
       </c>
     </row>
@@ -5420,9 +4039,6 @@
         <v>44652</v>
       </c>
       <c r="B461" t="n">
-        <v>0.461716666666667</v>
-      </c>
-      <c r="C461" t="n">
         <v>6.89691805555556</v>
       </c>
     </row>
@@ -5431,9 +4047,6 @@
         <v>44682</v>
       </c>
       <c r="B462" t="n">
-        <v>0.541469086021505</v>
-      </c>
-      <c r="C462" t="n">
         <v>7.49061827956989</v>
       </c>
     </row>
@@ -5442,9 +4055,6 @@
         <v>44713</v>
       </c>
       <c r="B463" t="n">
-        <v>0.511783333333333</v>
-      </c>
-      <c r="C463" t="n">
         <v>7.31596111111111</v>
       </c>
     </row>
@@ -5453,9 +4063,6 @@
         <v>44743</v>
       </c>
       <c r="B464" t="n">
-        <v>0.719405913978495</v>
-      </c>
-      <c r="C464" t="n">
         <v>8.96283198924731</v>
       </c>
     </row>
@@ -5464,9 +4071,6 @@
         <v>44774</v>
       </c>
       <c r="B465" t="n">
-        <v>0.727139784946237</v>
-      </c>
-      <c r="C465" t="n">
         <v>8.99873521505376</v>
       </c>
     </row>
@@ -5475,9 +4079,6 @@
         <v>44805</v>
       </c>
       <c r="B466" t="n">
-        <v>0.687340277777778</v>
-      </c>
-      <c r="C466" t="n">
         <v>8.58009166666667</v>
       </c>
     </row>
@@ -5486,9 +4087,6 @@
         <v>44835</v>
       </c>
       <c r="B467" t="n">
-        <v>0.685581989247312</v>
-      </c>
-      <c r="C467" t="n">
         <v>8.59481182795699</v>
       </c>
     </row>
@@ -5497,9 +4095,6 @@
         <v>44866</v>
       </c>
       <c r="B468" t="n">
-        <v>0.460105555555556</v>
-      </c>
-      <c r="C468" t="n">
         <v>6.93308055555556</v>
       </c>
     </row>
@@ -5508,9 +4103,6 @@
         <v>44896</v>
       </c>
       <c r="B469" t="n">
-        <v>0.523521505376344</v>
-      </c>
-      <c r="C469" t="n">
         <v>7.39595833333333</v>
       </c>
     </row>
@@ -5519,9 +4111,6 @@
         <v>44927</v>
       </c>
       <c r="B470" t="n">
-        <v>0.527622311827957</v>
-      </c>
-      <c r="C470" t="n">
         <v>7.39284005376344</v>
       </c>
     </row>
@@ -5530,9 +4119,6 @@
         <v>44958</v>
       </c>
       <c r="B471" t="n">
-        <v>0.553264880952381</v>
-      </c>
-      <c r="C471" t="n">
         <v>7.58038095238095</v>
       </c>
     </row>
@@ -5541,9 +4127,6 @@
         <v>44986</v>
       </c>
       <c r="B472" t="n">
-        <v>0.449194892473118</v>
-      </c>
-      <c r="C472" t="n">
         <v>6.75906451612903</v>
       </c>
     </row>
@@ -5552,9 +4135,6 @@
         <v>45017</v>
       </c>
       <c r="B473" t="n">
-        <v>0.392058333333333</v>
-      </c>
-      <c r="C473" t="n">
         <v>6.39270138888889</v>
       </c>
     </row>
@@ -5563,9 +4143,6 @@
         <v>45047</v>
       </c>
       <c r="B474" t="n">
-        <v>0.505275537634409</v>
-      </c>
-      <c r="C474" t="n">
         <v>7.26758870967742</v>
       </c>
     </row>
@@ -5574,9 +4151,6 @@
         <v>45078</v>
       </c>
       <c r="B475" t="n">
-        <v>0.650752777777778</v>
-      </c>
-      <c r="C475" t="n">
         <v>8.3591</v>
       </c>
     </row>
@@ -5585,9 +4159,6 @@
         <v>45108</v>
       </c>
       <c r="B476" t="n">
-        <v>0.66404435483871</v>
-      </c>
-      <c r="C476" t="n">
         <v>8.49490053763441</v>
       </c>
     </row>
@@ -5596,9 +4167,6 @@
         <v>45139</v>
       </c>
       <c r="B477" t="n">
-        <v>0.639333333333333</v>
-      </c>
-      <c r="C477" t="n">
         <v>8.26107392473118</v>
       </c>
     </row>
@@ -5607,9 +4175,6 @@
         <v>45170</v>
       </c>
       <c r="B478" t="n">
-        <v>0.708054166666667</v>
-      </c>
-      <c r="C478" t="n">
         <v>8.82719583333333</v>
       </c>
     </row>
@@ -5618,9 +4183,6 @@
         <v>45200</v>
       </c>
       <c r="B479" t="n">
-        <v>0.647909946236559</v>
-      </c>
-      <c r="C479" t="n">
         <v>8.29941397849462</v>
       </c>
     </row>
@@ -5629,9 +4191,6 @@
         <v>45231</v>
       </c>
       <c r="B480" t="n">
-        <v>0.575198611111111</v>
-      </c>
-      <c r="C480" t="n">
         <v>7.77758888888889</v>
       </c>
     </row>
@@ -5640,9 +4199,6 @@
         <v>45261</v>
       </c>
       <c r="B481" t="n">
-        <v>0.53159811827957</v>
-      </c>
-      <c r="C481" t="n">
         <v>7.43849059139785</v>
       </c>
     </row>
